--- a/tiflow-bfarm/main/2.0.0-ballot.2/StructureDefinition-erp-tprescription-medication-request.xlsx
+++ b/tiflow-bfarm/main/2.0.0-ballot.2/StructureDefinition-erp-tprescription-medication-request.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7332" uniqueCount="959">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7308" uniqueCount="957">
   <si>
     <t>Property</t>
   </si>
@@ -791,20 +791,10 @@
     <t>The value of the numerator.</t>
   </si>
   <si>
-    <t>The context of use may frequently define what kind of quantity this is and therefore what kind of units can be used. The context of use may also restrict the values for the comparator.</t>
-  </si>
-  <si>
     <t>Ratio.numerator</t>
   </si>
   <si>
-    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
-qty-3:If a code for the unit is present, the system SHALL also be present {code.empty() or system.exists()}</t>
-  </si>
-  <si>
     <t>.numerator</t>
-  </si>
-  <si>
-    <t>SN (see also Range) or CQ</t>
   </si>
   <si>
     <t>MedicationRequest.extension:multiplePrescription.extension:counter.value[x].numerator.id</t>
@@ -898,9 +888,6 @@
     <t>A human-readable form of the unit.</t>
   </si>
   <si>
-    <t>Note that FHIR strings SHALL NOT exceed 1MB in size</t>
-  </si>
-  <si>
     <t>There are many representations for units of measure and in many contexts, particular representations are fixed and required. I.e. mcg for micrograms.</t>
   </si>
   <si>
@@ -923,9 +910,6 @@
   </si>
   <si>
     <t>The identification of the system that provides the coded form of the unit.</t>
-  </si>
-  <si>
-    <t>see http://en.wikipedia.org/wiki/Uniform_resource_identifier</t>
   </si>
   <si>
     <t>Need to know the system that defines the coded form of the unit.</t>
@@ -1209,7 +1193,7 @@
     <t>A coded type for an identifier that can be used to determine which identifier to use for a specific purpose.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/identifier-type</t>
+    <t>http://hl7.org/fhir/ValueSet/identifier-type|4.0.1</t>
   </si>
   <si>
     <t>Identifier.type</t>
@@ -1290,17 +1274,9 @@
     <t>Time period during which identifier is/was valid for use.</t>
   </si>
   <si>
-    <t>A Period specifies a range of time; the context of use will specify whether the entire range applies (e.g. "the patient was an inpatient of the hospital for this time range") or one value from the range applies (e.g. "give to the patient between these two times").
-Period is not used for a duration (a measure of elapsed time). See [Duration](http://hl7.org/fhir/R4/datatypes.html#Duration).</t>
-  </si>
-  <si>
     <t>Identifier.period</t>
   </si>
   <si>
-    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
-per-1:If present, start SHALL have a lower value than end {start.hasValue().not() or end.hasValue().not() or (start &lt;= end)}</t>
-  </si>
-  <si>
     <t>Role.effectiveTime or implied by context</t>
   </si>
   <si>
@@ -1313,7 +1289,7 @@
     <t>MedicationRequest.extension.extension.value[x].assigner</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Organization)
+    <t xml:space="preserve">Reference(Organization|4.0.1)
 </t>
   </si>
   <si>
@@ -1327,10 +1303,6 @@
   </si>
   <si>
     <t>Identifier.assigner</t>
-  </si>
-  <si>
-    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
-ref-1:SHALL have a contained resource if a local reference is provided {reference.startsWith('#').not() or (reference.substring(1).trace('url') in %rootResource.contained.id.trace('ids'))}</t>
   </si>
   <si>
     <t>II.assigningAuthorityName but note that this is an improper use by the definition of the field.  Also Role.scoper</t>
@@ -2083,6 +2055,10 @@
     <t>The subject on a medication request is mandatory.  For the secondary use case where the actual subject is not provided, there still must be an anonymized subject specified.</t>
   </si>
   <si>
+    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+ref-1:SHALL have a contained resource if a local reference is provided {reference.startsWith('#').not() or (reference.substring(1).trace('url') in %rootResource.contained.id.trace('ids'))}</t>
+  </si>
+  <si>
     <t>Request.subject</t>
   </si>
   <si>
@@ -2426,6 +2402,9 @@
   </si>
   <si>
     <t>The URL pointing to an externally maintained protocol, guideline, orderset or other definition that is adhered to in whole or in part by this MedicationRequest.</t>
+  </si>
+  <si>
+    <t>see http://en.wikipedia.org/wiki/Uniform_resource_identifier</t>
   </si>
   <si>
     <t>MedicationRequest.basedOn</t>
@@ -2824,6 +2803,9 @@
     <t>The amount or quantity to provide as part of the first dispense.</t>
   </si>
   <si>
+    <t>The context of use may frequently define what kind of quantity this is and therefore what kind of units can be used. The context of use may also restrict the values for the comparator.</t>
+  </si>
+  <si>
     <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
 qty-3:If a code for the unit is present, the system SHALL also be present {code.empty() or system.exists()}sqty-1:The comparator is not used on a SimpleQuantity {comparator.empty()}</t>
   </si>
@@ -2831,6 +2813,9 @@
     <t>Supply.quantity[moodCode=RQO]</t>
   </si>
   <si>
+    <t>SN (see also Range) or CQ</t>
+  </si>
+  <si>
     <t>MedicationRequest.dispenseRequest.initialFill.duration</t>
   </si>
   <si>
@@ -2875,6 +2860,10 @@
     <t>Indicates when the Prescription becomes valid, and when it ceases to be a dispensable Prescription.</t>
   </si>
   <si>
+    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+per-1:If present, start SHALL have a lower value than end {start.hasValue().not() or end.hasValue().not() or (start &lt;= end)}</t>
+  </si>
+  <si>
     <t>Message/Body/NewRx/MedicationPrescribed/Refills</t>
   </si>
   <si>
@@ -2976,6 +2965,10 @@
   </si>
   <si>
     <t>MedicationRequest.dispenseRequest.performer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reference(Organization)
+</t>
   </si>
   <si>
     <t>Intended dispenser</t>
@@ -5697,7 +5690,7 @@
         <v>81</v>
       </c>
       <c r="AM19" t="s" s="2">
-        <v>108</v>
+        <v>192</v>
       </c>
       <c r="AN19" t="s" s="2">
         <v>81</v>
@@ -5830,7 +5823,7 @@
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
-        <v>110</v>
+        <v>81</v>
       </c>
       <c r="E21" s="2"/>
       <c r="F21" t="s" s="2">
@@ -5852,14 +5845,12 @@
         <v>111</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>112</v>
+        <v>194</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>113</v>
-      </c>
-      <c r="N21" t="s" s="2">
-        <v>114</v>
-      </c>
+        <v>195</v>
+      </c>
+      <c r="N21" s="2"/>
       <c r="O21" s="2"/>
       <c r="P21" t="s" s="2">
         <v>81</v>
@@ -5929,7 +5920,7 @@
         <v>81</v>
       </c>
       <c r="AM21" t="s" s="2">
-        <v>108</v>
+        <v>81</v>
       </c>
       <c r="AN21" t="s" s="2">
         <v>81</v>
@@ -5949,7 +5940,7 @@
         <v>213</v>
       </c>
       <c r="D22" t="s" s="2">
-        <v>110</v>
+        <v>81</v>
       </c>
       <c r="E22" s="2"/>
       <c r="F22" t="s" s="2">
@@ -5971,14 +5962,12 @@
         <v>111</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>112</v>
+        <v>194</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>113</v>
-      </c>
-      <c r="N22" t="s" s="2">
-        <v>114</v>
-      </c>
+        <v>195</v>
+      </c>
+      <c r="N22" s="2"/>
       <c r="O22" s="2"/>
       <c r="P22" t="s" s="2">
         <v>81</v>
@@ -6048,7 +6037,7 @@
         <v>81</v>
       </c>
       <c r="AM22" t="s" s="2">
-        <v>108</v>
+        <v>81</v>
       </c>
       <c r="AN22" t="s" s="2">
         <v>81</v>
@@ -6181,7 +6170,7 @@
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
-        <v>110</v>
+        <v>81</v>
       </c>
       <c r="E24" s="2"/>
       <c r="F24" t="s" s="2">
@@ -6203,14 +6192,12 @@
         <v>111</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>112</v>
+        <v>194</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>113</v>
-      </c>
-      <c r="N24" t="s" s="2">
-        <v>114</v>
-      </c>
+        <v>195</v>
+      </c>
+      <c r="N24" s="2"/>
       <c r="O24" s="2"/>
       <c r="P24" t="s" s="2">
         <v>81</v>
@@ -6280,7 +6267,7 @@
         <v>81</v>
       </c>
       <c r="AM24" t="s" s="2">
-        <v>108</v>
+        <v>81</v>
       </c>
       <c r="AN24" t="s" s="2">
         <v>81</v>
@@ -6500,7 +6487,7 @@
         <v>90</v>
       </c>
       <c r="AI26" t="s" s="2">
-        <v>152</v>
+        <v>81</v>
       </c>
       <c r="AJ26" t="s" s="2">
         <v>102</v>
@@ -6532,7 +6519,7 @@
         <v>231</v>
       </c>
       <c r="D27" t="s" s="2">
-        <v>110</v>
+        <v>81</v>
       </c>
       <c r="E27" s="2"/>
       <c r="F27" t="s" s="2">
@@ -6554,14 +6541,12 @@
         <v>111</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>112</v>
+        <v>194</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>113</v>
-      </c>
-      <c r="N27" t="s" s="2">
-        <v>114</v>
-      </c>
+        <v>195</v>
+      </c>
+      <c r="N27" s="2"/>
       <c r="O27" s="2"/>
       <c r="P27" t="s" s="2">
         <v>81</v>
@@ -6631,7 +6616,7 @@
         <v>81</v>
       </c>
       <c r="AM27" t="s" s="2">
-        <v>108</v>
+        <v>81</v>
       </c>
       <c r="AN27" t="s" s="2">
         <v>81</v>
@@ -6764,7 +6749,7 @@
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
-        <v>110</v>
+        <v>81</v>
       </c>
       <c r="E29" s="2"/>
       <c r="F29" t="s" s="2">
@@ -6786,14 +6771,12 @@
         <v>111</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>112</v>
+        <v>194</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>113</v>
-      </c>
-      <c r="N29" t="s" s="2">
-        <v>114</v>
-      </c>
+        <v>195</v>
+      </c>
+      <c r="N29" s="2"/>
       <c r="O29" s="2"/>
       <c r="P29" t="s" s="2">
         <v>81</v>
@@ -6863,7 +6846,7 @@
         <v>81</v>
       </c>
       <c r="AM29" t="s" s="2">
-        <v>108</v>
+        <v>81</v>
       </c>
       <c r="AN29" t="s" s="2">
         <v>81</v>
@@ -7083,7 +7066,7 @@
         <v>90</v>
       </c>
       <c r="AI31" t="s" s="2">
-        <v>152</v>
+        <v>81</v>
       </c>
       <c r="AJ31" t="s" s="2">
         <v>102</v>
@@ -7372,9 +7355,7 @@
       <c r="M34" t="s" s="2">
         <v>247</v>
       </c>
-      <c r="N34" t="s" s="2">
-        <v>248</v>
-      </c>
+      <c r="N34" s="2"/>
       <c r="O34" s="2"/>
       <c r="P34" t="s" s="2">
         <v>81</v>
@@ -7423,42 +7404,42 @@
         <v>81</v>
       </c>
       <c r="AF34" t="s" s="2">
+        <v>248</v>
+      </c>
+      <c r="AG34" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH34" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="AI34" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AJ34" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="AK34" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AL34" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AM34" t="s" s="2">
         <v>249</v>
       </c>
-      <c r="AG34" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AH34" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="AI34" t="s" s="2">
-        <v>152</v>
-      </c>
-      <c r="AJ34" t="s" s="2">
-        <v>250</v>
-      </c>
-      <c r="AK34" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AL34" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AM34" t="s" s="2">
-        <v>251</v>
-      </c>
       <c r="AN34" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AO34" t="s" s="2">
-        <v>252</v>
+        <v>81</v>
       </c>
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>253</v>
+        <v>250</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>254</v>
+        <v>251</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -7570,10 +7551,10 @@
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>255</v>
+        <v>252</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>256</v>
+        <v>253</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -7687,10 +7668,10 @@
     </row>
     <row r="37">
       <c r="A37" t="s" s="2">
-        <v>257</v>
+        <v>254</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>258</v>
+        <v>255</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -7713,19 +7694,19 @@
         <v>91</v>
       </c>
       <c r="K37" t="s" s="2">
+        <v>256</v>
+      </c>
+      <c r="L37" t="s" s="2">
+        <v>257</v>
+      </c>
+      <c r="M37" t="s" s="2">
+        <v>258</v>
+      </c>
+      <c r="N37" t="s" s="2">
         <v>259</v>
       </c>
-      <c r="L37" t="s" s="2">
+      <c r="O37" t="s" s="2">
         <v>260</v>
-      </c>
-      <c r="M37" t="s" s="2">
-        <v>261</v>
-      </c>
-      <c r="N37" t="s" s="2">
-        <v>262</v>
-      </c>
-      <c r="O37" t="s" s="2">
-        <v>263</v>
       </c>
       <c r="P37" t="s" s="2">
         <v>81</v>
@@ -7774,7 +7755,7 @@
         <v>81</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>264</v>
+        <v>261</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>79</v>
@@ -7795,21 +7776,21 @@
         <v>81</v>
       </c>
       <c r="AM37" t="s" s="2">
-        <v>265</v>
+        <v>262</v>
       </c>
       <c r="AN37" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AO37" t="s" s="2">
-        <v>266</v>
+        <v>263</v>
       </c>
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>267</v>
+        <v>264</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>268</v>
+        <v>265</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -7835,65 +7816,65 @@
         <v>169</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>269</v>
+        <v>266</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>270</v>
+        <v>267</v>
       </c>
       <c r="N38" s="2"/>
       <c r="O38" t="s" s="2">
+        <v>268</v>
+      </c>
+      <c r="P38" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Q38" t="s" s="2">
+        <v>269</v>
+      </c>
+      <c r="R38" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="S38" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="T38" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="U38" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="V38" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="W38" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="X38" t="s" s="2">
+        <v>270</v>
+      </c>
+      <c r="Y38" t="s" s="2">
         <v>271</v>
       </c>
-      <c r="P38" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Q38" t="s" s="2">
+      <c r="Z38" t="s" s="2">
         <v>272</v>
       </c>
-      <c r="R38" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="S38" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="T38" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="U38" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="V38" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="W38" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="X38" t="s" s="2">
+      <c r="AA38" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AB38" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AC38" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AD38" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AE38" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AF38" t="s" s="2">
         <v>273</v>
-      </c>
-      <c r="Y38" t="s" s="2">
-        <v>274</v>
-      </c>
-      <c r="Z38" t="s" s="2">
-        <v>275</v>
-      </c>
-      <c r="AA38" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AB38" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AC38" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AD38" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AE38" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AF38" t="s" s="2">
-        <v>276</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>79</v>
@@ -7914,21 +7895,21 @@
         <v>81</v>
       </c>
       <c r="AM38" t="s" s="2">
-        <v>277</v>
+        <v>274</v>
       </c>
       <c r="AN38" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AO38" t="s" s="2">
-        <v>278</v>
+        <v>275</v>
       </c>
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>279</v>
+        <v>276</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>280</v>
+        <v>277</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -7954,16 +7935,14 @@
         <v>104</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>281</v>
+        <v>278</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>282</v>
-      </c>
-      <c r="N39" t="s" s="2">
-        <v>283</v>
-      </c>
+        <v>279</v>
+      </c>
+      <c r="N39" s="2"/>
       <c r="O39" t="s" s="2">
-        <v>284</v>
+        <v>280</v>
       </c>
       <c r="P39" t="s" s="2">
         <v>81</v>
@@ -8012,7 +7991,7 @@
         <v>81</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>285</v>
+        <v>281</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>79</v>
@@ -8033,21 +8012,21 @@
         <v>81</v>
       </c>
       <c r="AM39" t="s" s="2">
-        <v>286</v>
+        <v>282</v>
       </c>
       <c r="AN39" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AO39" t="s" s="2">
-        <v>287</v>
+        <v>283</v>
       </c>
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>288</v>
+        <v>284</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>289</v>
+        <v>285</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -8073,16 +8052,14 @@
         <v>132</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>290</v>
+        <v>286</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>291</v>
-      </c>
-      <c r="N40" t="s" s="2">
-        <v>292</v>
-      </c>
+        <v>287</v>
+      </c>
+      <c r="N40" s="2"/>
       <c r="O40" t="s" s="2">
-        <v>293</v>
+        <v>288</v>
       </c>
       <c r="P40" t="s" s="2">
         <v>81</v>
@@ -8131,7 +8108,7 @@
         <v>81</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>294</v>
+        <v>289</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>79</v>
@@ -8140,7 +8117,7 @@
         <v>90</v>
       </c>
       <c r="AI40" t="s" s="2">
-        <v>295</v>
+        <v>290</v>
       </c>
       <c r="AJ40" t="s" s="2">
         <v>102</v>
@@ -8152,21 +8129,21 @@
         <v>81</v>
       </c>
       <c r="AM40" t="s" s="2">
-        <v>296</v>
+        <v>291</v>
       </c>
       <c r="AN40" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AO40" t="s" s="2">
-        <v>287</v>
+        <v>283</v>
       </c>
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>297</v>
+        <v>292</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>298</v>
+        <v>293</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -8192,16 +8169,16 @@
         <v>169</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>299</v>
+        <v>294</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>300</v>
+        <v>295</v>
       </c>
       <c r="N41" t="s" s="2">
-        <v>301</v>
+        <v>296</v>
       </c>
       <c r="O41" t="s" s="2">
-        <v>302</v>
+        <v>297</v>
       </c>
       <c r="P41" t="s" s="2">
         <v>81</v>
@@ -8250,7 +8227,7 @@
         <v>81</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>303</v>
+        <v>298</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>79</v>
@@ -8271,21 +8248,21 @@
         <v>81</v>
       </c>
       <c r="AM41" t="s" s="2">
-        <v>304</v>
+        <v>299</v>
       </c>
       <c r="AN41" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AO41" t="s" s="2">
-        <v>287</v>
+        <v>283</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="s" s="2">
-        <v>305</v>
+        <v>300</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>306</v>
+        <v>301</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -8311,14 +8288,12 @@
         <v>245</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>307</v>
+        <v>302</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>308</v>
-      </c>
-      <c r="N42" t="s" s="2">
-        <v>248</v>
-      </c>
+        <v>303</v>
+      </c>
+      <c r="N42" s="2"/>
       <c r="O42" s="2"/>
       <c r="P42" t="s" s="2">
         <v>81</v>
@@ -8367,7 +8342,7 @@
         <v>81</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>309</v>
+        <v>304</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>79</v>
@@ -8376,10 +8351,10 @@
         <v>90</v>
       </c>
       <c r="AI42" t="s" s="2">
-        <v>152</v>
+        <v>81</v>
       </c>
       <c r="AJ42" t="s" s="2">
-        <v>250</v>
+        <v>102</v>
       </c>
       <c r="AK42" t="s" s="2">
         <v>81</v>
@@ -8388,21 +8363,21 @@
         <v>81</v>
       </c>
       <c r="AM42" t="s" s="2">
-        <v>310</v>
+        <v>305</v>
       </c>
       <c r="AN42" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AO42" t="s" s="2">
-        <v>252</v>
+        <v>81</v>
       </c>
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>311</v>
+        <v>306</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>312</v>
+        <v>307</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -8514,10 +8489,10 @@
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>313</v>
+        <v>308</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>314</v>
+        <v>309</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -8631,10 +8606,10 @@
     </row>
     <row r="45">
       <c r="A45" t="s" s="2">
-        <v>315</v>
+        <v>310</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>316</v>
+        <v>311</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -8657,19 +8632,19 @@
         <v>91</v>
       </c>
       <c r="K45" t="s" s="2">
+        <v>256</v>
+      </c>
+      <c r="L45" t="s" s="2">
+        <v>312</v>
+      </c>
+      <c r="M45" t="s" s="2">
+        <v>313</v>
+      </c>
+      <c r="N45" t="s" s="2">
         <v>259</v>
       </c>
-      <c r="L45" t="s" s="2">
-        <v>317</v>
-      </c>
-      <c r="M45" t="s" s="2">
-        <v>318</v>
-      </c>
-      <c r="N45" t="s" s="2">
-        <v>262</v>
-      </c>
       <c r="O45" t="s" s="2">
-        <v>263</v>
+        <v>260</v>
       </c>
       <c r="P45" t="s" s="2">
         <v>81</v>
@@ -8718,7 +8693,7 @@
         <v>81</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>264</v>
+        <v>261</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>79</v>
@@ -8739,21 +8714,21 @@
         <v>81</v>
       </c>
       <c r="AM45" t="s" s="2">
-        <v>265</v>
+        <v>262</v>
       </c>
       <c r="AN45" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AO45" t="s" s="2">
-        <v>266</v>
+        <v>263</v>
       </c>
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>319</v>
+        <v>314</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>320</v>
+        <v>315</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -8779,65 +8754,65 @@
         <v>169</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>269</v>
+        <v>266</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>270</v>
+        <v>267</v>
       </c>
       <c r="N46" s="2"/>
       <c r="O46" t="s" s="2">
+        <v>268</v>
+      </c>
+      <c r="P46" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Q46" t="s" s="2">
+        <v>269</v>
+      </c>
+      <c r="R46" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="S46" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="T46" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="U46" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="V46" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="W46" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="X46" t="s" s="2">
+        <v>270</v>
+      </c>
+      <c r="Y46" t="s" s="2">
         <v>271</v>
       </c>
-      <c r="P46" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Q46" t="s" s="2">
+      <c r="Z46" t="s" s="2">
         <v>272</v>
       </c>
-      <c r="R46" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="S46" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="T46" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="U46" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="V46" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="W46" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="X46" t="s" s="2">
+      <c r="AA46" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AB46" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AC46" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AD46" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AE46" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AF46" t="s" s="2">
         <v>273</v>
-      </c>
-      <c r="Y46" t="s" s="2">
-        <v>274</v>
-      </c>
-      <c r="Z46" t="s" s="2">
-        <v>275</v>
-      </c>
-      <c r="AA46" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AB46" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AC46" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AD46" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AE46" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AF46" t="s" s="2">
-        <v>276</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>79</v>
@@ -8858,21 +8833,21 @@
         <v>81</v>
       </c>
       <c r="AM46" t="s" s="2">
-        <v>277</v>
+        <v>274</v>
       </c>
       <c r="AN46" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AO46" t="s" s="2">
-        <v>278</v>
+        <v>275</v>
       </c>
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>321</v>
+        <v>316</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>322</v>
+        <v>317</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -8898,16 +8873,14 @@
         <v>104</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>281</v>
+        <v>278</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>282</v>
-      </c>
-      <c r="N47" t="s" s="2">
-        <v>283</v>
-      </c>
+        <v>279</v>
+      </c>
+      <c r="N47" s="2"/>
       <c r="O47" t="s" s="2">
-        <v>284</v>
+        <v>280</v>
       </c>
       <c r="P47" t="s" s="2">
         <v>81</v>
@@ -8956,7 +8929,7 @@
         <v>81</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>285</v>
+        <v>281</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>79</v>
@@ -8977,21 +8950,21 @@
         <v>81</v>
       </c>
       <c r="AM47" t="s" s="2">
-        <v>286</v>
+        <v>282</v>
       </c>
       <c r="AN47" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AO47" t="s" s="2">
-        <v>287</v>
+        <v>283</v>
       </c>
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>323</v>
+        <v>318</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>324</v>
+        <v>319</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -9017,16 +8990,14 @@
         <v>132</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>290</v>
+        <v>286</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>291</v>
-      </c>
-      <c r="N48" t="s" s="2">
-        <v>292</v>
-      </c>
+        <v>287</v>
+      </c>
+      <c r="N48" s="2"/>
       <c r="O48" t="s" s="2">
-        <v>293</v>
+        <v>288</v>
       </c>
       <c r="P48" t="s" s="2">
         <v>81</v>
@@ -9075,7 +9046,7 @@
         <v>81</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>294</v>
+        <v>289</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>79</v>
@@ -9084,7 +9055,7 @@
         <v>90</v>
       </c>
       <c r="AI48" t="s" s="2">
-        <v>295</v>
+        <v>290</v>
       </c>
       <c r="AJ48" t="s" s="2">
         <v>102</v>
@@ -9096,21 +9067,21 @@
         <v>81</v>
       </c>
       <c r="AM48" t="s" s="2">
-        <v>296</v>
+        <v>291</v>
       </c>
       <c r="AN48" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AO48" t="s" s="2">
-        <v>287</v>
+        <v>283</v>
       </c>
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>325</v>
+        <v>320</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>326</v>
+        <v>321</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -9136,16 +9107,16 @@
         <v>169</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>299</v>
+        <v>294</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>300</v>
+        <v>295</v>
       </c>
       <c r="N49" t="s" s="2">
-        <v>301</v>
+        <v>296</v>
       </c>
       <c r="O49" t="s" s="2">
-        <v>302</v>
+        <v>297</v>
       </c>
       <c r="P49" t="s" s="2">
         <v>81</v>
@@ -9194,7 +9165,7 @@
         <v>81</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>303</v>
+        <v>298</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>79</v>
@@ -9215,27 +9186,27 @@
         <v>81</v>
       </c>
       <c r="AM49" t="s" s="2">
-        <v>304</v>
+        <v>299</v>
       </c>
       <c r="AN49" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AO49" t="s" s="2">
-        <v>287</v>
+        <v>283</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="s" s="2">
-        <v>327</v>
+        <v>322</v>
       </c>
       <c r="B50" t="s" s="2">
         <v>210</v>
       </c>
       <c r="C50" t="s" s="2">
-        <v>328</v>
+        <v>323</v>
       </c>
       <c r="D50" t="s" s="2">
-        <v>110</v>
+        <v>81</v>
       </c>
       <c r="E50" s="2"/>
       <c r="F50" t="s" s="2">
@@ -9257,14 +9228,12 @@
         <v>111</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>329</v>
+        <v>324</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>113</v>
-      </c>
-      <c r="N50" t="s" s="2">
-        <v>114</v>
-      </c>
+        <v>195</v>
+      </c>
+      <c r="N50" s="2"/>
       <c r="O50" s="2"/>
       <c r="P50" t="s" s="2">
         <v>81</v>
@@ -9334,7 +9303,7 @@
         <v>81</v>
       </c>
       <c r="AM50" t="s" s="2">
-        <v>108</v>
+        <v>81</v>
       </c>
       <c r="AN50" t="s" s="2">
         <v>81</v>
@@ -9345,7 +9314,7 @@
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>330</v>
+        <v>325</v>
       </c>
       <c r="B51" t="s" s="2">
         <v>215</v>
@@ -9460,14 +9429,14 @@
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>331</v>
+        <v>326</v>
       </c>
       <c r="B52" t="s" s="2">
         <v>217</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
-        <v>110</v>
+        <v>81</v>
       </c>
       <c r="E52" s="2"/>
       <c r="F52" t="s" s="2">
@@ -9489,14 +9458,12 @@
         <v>111</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>112</v>
+        <v>194</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>113</v>
-      </c>
-      <c r="N52" t="s" s="2">
-        <v>114</v>
-      </c>
+        <v>195</v>
+      </c>
+      <c r="N52" s="2"/>
       <c r="O52" s="2"/>
       <c r="P52" t="s" s="2">
         <v>81</v>
@@ -9566,7 +9533,7 @@
         <v>81</v>
       </c>
       <c r="AM52" t="s" s="2">
-        <v>108</v>
+        <v>81</v>
       </c>
       <c r="AN52" t="s" s="2">
         <v>81</v>
@@ -9577,7 +9544,7 @@
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>332</v>
+        <v>327</v>
       </c>
       <c r="B53" t="s" s="2">
         <v>219</v>
@@ -9620,7 +9587,7 @@
       </c>
       <c r="Q53" s="2"/>
       <c r="R53" t="s" s="2">
-        <v>328</v>
+        <v>323</v>
       </c>
       <c r="S53" t="s" s="2">
         <v>81</v>
@@ -9694,7 +9661,7 @@
     </row>
     <row r="54">
       <c r="A54" t="s" s="2">
-        <v>333</v>
+        <v>328</v>
       </c>
       <c r="B54" t="s" s="2">
         <v>225</v>
@@ -9720,7 +9687,7 @@
         <v>81</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>334</v>
+        <v>329</v>
       </c>
       <c r="L54" t="s" s="2">
         <v>237</v>
@@ -9786,10 +9753,10 @@
         <v>90</v>
       </c>
       <c r="AI54" t="s" s="2">
-        <v>152</v>
+        <v>81</v>
       </c>
       <c r="AJ54" t="s" s="2">
-        <v>335</v>
+        <v>330</v>
       </c>
       <c r="AK54" t="s" s="2">
         <v>81</v>
@@ -9809,7 +9776,7 @@
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>336</v>
+        <v>331</v>
       </c>
       <c r="B55" t="s" s="2">
         <v>240</v>
@@ -9924,7 +9891,7 @@
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>337</v>
+        <v>332</v>
       </c>
       <c r="B56" t="s" s="2">
         <v>242</v>
@@ -10041,10 +10008,10 @@
     </row>
     <row r="57">
       <c r="A57" t="s" s="2">
-        <v>338</v>
+        <v>333</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>339</v>
+        <v>334</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -10067,16 +10034,16 @@
         <v>91</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>340</v>
+        <v>335</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>341</v>
+        <v>336</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>342</v>
+        <v>337</v>
       </c>
       <c r="N57" t="s" s="2">
-        <v>343</v>
+        <v>338</v>
       </c>
       <c r="O57" s="2"/>
       <c r="P57" t="s" s="2">
@@ -10126,7 +10093,7 @@
         <v>81</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>344</v>
+        <v>339</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>79</v>
@@ -10135,7 +10102,7 @@
         <v>90</v>
       </c>
       <c r="AI57" t="s" s="2">
-        <v>345</v>
+        <v>340</v>
       </c>
       <c r="AJ57" t="s" s="2">
         <v>102</v>
@@ -10147,21 +10114,21 @@
         <v>81</v>
       </c>
       <c r="AM57" t="s" s="2">
-        <v>346</v>
+        <v>341</v>
       </c>
       <c r="AN57" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AO57" t="s" s="2">
-        <v>347</v>
+        <v>342</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="s" s="2">
-        <v>348</v>
+        <v>343</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>349</v>
+        <v>344</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -10184,23 +10151,23 @@
         <v>91</v>
       </c>
       <c r="K58" t="s" s="2">
-        <v>340</v>
+        <v>335</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>350</v>
+        <v>345</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>351</v>
+        <v>346</v>
       </c>
       <c r="N58" t="s" s="2">
-        <v>352</v>
+        <v>347</v>
       </c>
       <c r="O58" s="2"/>
       <c r="P58" t="s" s="2">
         <v>81</v>
       </c>
       <c r="Q58" t="s" s="2">
-        <v>353</v>
+        <v>348</v>
       </c>
       <c r="R58" t="s" s="2">
         <v>81</v>
@@ -10245,7 +10212,7 @@
         <v>81</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>354</v>
+        <v>349</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>79</v>
@@ -10254,7 +10221,7 @@
         <v>90</v>
       </c>
       <c r="AI58" t="s" s="2">
-        <v>345</v>
+        <v>340</v>
       </c>
       <c r="AJ58" t="s" s="2">
         <v>102</v>
@@ -10266,27 +10233,27 @@
         <v>81</v>
       </c>
       <c r="AM58" t="s" s="2">
-        <v>355</v>
+        <v>350</v>
       </c>
       <c r="AN58" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AO58" t="s" s="2">
-        <v>356</v>
+        <v>351</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="s" s="2">
-        <v>357</v>
+        <v>352</v>
       </c>
       <c r="B59" t="s" s="2">
         <v>210</v>
       </c>
       <c r="C59" t="s" s="2">
-        <v>358</v>
+        <v>353</v>
       </c>
       <c r="D59" t="s" s="2">
-        <v>110</v>
+        <v>81</v>
       </c>
       <c r="E59" s="2"/>
       <c r="F59" t="s" s="2">
@@ -10308,14 +10275,12 @@
         <v>111</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>112</v>
+        <v>194</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>113</v>
-      </c>
-      <c r="N59" t="s" s="2">
-        <v>114</v>
-      </c>
+        <v>195</v>
+      </c>
+      <c r="N59" s="2"/>
       <c r="O59" s="2"/>
       <c r="P59" t="s" s="2">
         <v>81</v>
@@ -10385,7 +10350,7 @@
         <v>81</v>
       </c>
       <c r="AM59" t="s" s="2">
-        <v>108</v>
+        <v>81</v>
       </c>
       <c r="AN59" t="s" s="2">
         <v>81</v>
@@ -10396,7 +10361,7 @@
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>359</v>
+        <v>354</v>
       </c>
       <c r="B60" t="s" s="2">
         <v>215</v>
@@ -10511,14 +10476,14 @@
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>360</v>
+        <v>355</v>
       </c>
       <c r="B61" t="s" s="2">
         <v>217</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
-        <v>110</v>
+        <v>81</v>
       </c>
       <c r="E61" s="2"/>
       <c r="F61" t="s" s="2">
@@ -10540,14 +10505,12 @@
         <v>111</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>112</v>
+        <v>194</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>113</v>
-      </c>
-      <c r="N61" t="s" s="2">
-        <v>114</v>
-      </c>
+        <v>195</v>
+      </c>
+      <c r="N61" s="2"/>
       <c r="O61" s="2"/>
       <c r="P61" t="s" s="2">
         <v>81</v>
@@ -10617,7 +10580,7 @@
         <v>81</v>
       </c>
       <c r="AM61" t="s" s="2">
-        <v>108</v>
+        <v>81</v>
       </c>
       <c r="AN61" t="s" s="2">
         <v>81</v>
@@ -10628,7 +10591,7 @@
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>361</v>
+        <v>356</v>
       </c>
       <c r="B62" t="s" s="2">
         <v>219</v>
@@ -10671,7 +10634,7 @@
       </c>
       <c r="Q62" s="2"/>
       <c r="R62" t="s" s="2">
-        <v>358</v>
+        <v>353</v>
       </c>
       <c r="S62" t="s" s="2">
         <v>81</v>
@@ -10745,7 +10708,7 @@
     </row>
     <row r="63">
       <c r="A63" t="s" s="2">
-        <v>362</v>
+        <v>357</v>
       </c>
       <c r="B63" t="s" s="2">
         <v>225</v>
@@ -10771,7 +10734,7 @@
         <v>81</v>
       </c>
       <c r="K63" t="s" s="2">
-        <v>363</v>
+        <v>358</v>
       </c>
       <c r="L63" t="s" s="2">
         <v>237</v>
@@ -10837,7 +10800,7 @@
         <v>90</v>
       </c>
       <c r="AI63" t="s" s="2">
-        <v>152</v>
+        <v>81</v>
       </c>
       <c r="AJ63" t="s" s="2">
         <v>102</v>
@@ -10860,7 +10823,7 @@
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>364</v>
+        <v>359</v>
       </c>
       <c r="B64" t="s" s="2">
         <v>240</v>
@@ -10975,7 +10938,7 @@
     </row>
     <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>365</v>
+        <v>360</v>
       </c>
       <c r="B65" t="s" s="2">
         <v>242</v>
@@ -11092,10 +11055,10 @@
     </row>
     <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>366</v>
+        <v>361</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>367</v>
+        <v>362</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -11121,16 +11084,16 @@
         <v>169</v>
       </c>
       <c r="L66" t="s" s="2">
-        <v>368</v>
+        <v>363</v>
       </c>
       <c r="M66" t="s" s="2">
-        <v>369</v>
+        <v>364</v>
       </c>
       <c r="N66" t="s" s="2">
-        <v>370</v>
+        <v>365</v>
       </c>
       <c r="O66" t="s" s="2">
-        <v>371</v>
+        <v>366</v>
       </c>
       <c r="P66" t="s" s="2">
         <v>81</v>
@@ -11155,13 +11118,13 @@
         <v>81</v>
       </c>
       <c r="X66" t="s" s="2">
-        <v>273</v>
+        <v>270</v>
       </c>
       <c r="Y66" t="s" s="2">
-        <v>372</v>
+        <v>367</v>
       </c>
       <c r="Z66" t="s" s="2">
-        <v>373</v>
+        <v>368</v>
       </c>
       <c r="AA66" t="s" s="2">
         <v>81</v>
@@ -11179,7 +11142,7 @@
         <v>81</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>374</v>
+        <v>369</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>79</v>
@@ -11200,7 +11163,7 @@
         <v>81</v>
       </c>
       <c r="AM66" t="s" s="2">
-        <v>375</v>
+        <v>370</v>
       </c>
       <c r="AN66" t="s" s="2">
         <v>81</v>
@@ -11211,10 +11174,10 @@
     </row>
     <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>376</v>
+        <v>371</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>377</v>
+        <v>372</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -11237,19 +11200,19 @@
         <v>91</v>
       </c>
       <c r="K67" t="s" s="2">
-        <v>378</v>
+        <v>373</v>
       </c>
       <c r="L67" t="s" s="2">
-        <v>379</v>
+        <v>374</v>
       </c>
       <c r="M67" t="s" s="2">
-        <v>380</v>
+        <v>375</v>
       </c>
       <c r="N67" t="s" s="2">
-        <v>381</v>
+        <v>376</v>
       </c>
       <c r="O67" t="s" s="2">
-        <v>382</v>
+        <v>377</v>
       </c>
       <c r="P67" t="s" s="2">
         <v>81</v>
@@ -11277,10 +11240,10 @@
         <v>148</v>
       </c>
       <c r="Y67" t="s" s="2">
-        <v>383</v>
+        <v>378</v>
       </c>
       <c r="Z67" t="s" s="2">
-        <v>384</v>
+        <v>379</v>
       </c>
       <c r="AA67" t="s" s="2">
         <v>81</v>
@@ -11298,7 +11261,7 @@
         <v>81</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>385</v>
+        <v>380</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>79</v>
@@ -11307,7 +11270,7 @@
         <v>90</v>
       </c>
       <c r="AI67" t="s" s="2">
-        <v>152</v>
+        <v>81</v>
       </c>
       <c r="AJ67" t="s" s="2">
         <v>102</v>
@@ -11319,21 +11282,21 @@
         <v>81</v>
       </c>
       <c r="AM67" t="s" s="2">
-        <v>375</v>
+        <v>370</v>
       </c>
       <c r="AN67" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AO67" t="s" s="2">
-        <v>386</v>
+        <v>381</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="s" s="2">
-        <v>387</v>
+        <v>382</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>388</v>
+        <v>383</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -11359,29 +11322,29 @@
         <v>132</v>
       </c>
       <c r="L68" t="s" s="2">
-        <v>389</v>
+        <v>384</v>
       </c>
       <c r="M68" t="s" s="2">
-        <v>390</v>
+        <v>385</v>
       </c>
       <c r="N68" t="s" s="2">
-        <v>391</v>
+        <v>386</v>
       </c>
       <c r="O68" t="s" s="2">
-        <v>392</v>
+        <v>387</v>
       </c>
       <c r="P68" t="s" s="2">
         <v>81</v>
       </c>
       <c r="Q68" s="2"/>
       <c r="R68" t="s" s="2">
-        <v>393</v>
+        <v>388</v>
       </c>
       <c r="S68" t="s" s="2">
         <v>81</v>
       </c>
       <c r="T68" t="s" s="2">
-        <v>394</v>
+        <v>389</v>
       </c>
       <c r="U68" t="s" s="2">
         <v>81</v>
@@ -11417,7 +11380,7 @@
         <v>81</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>395</v>
+        <v>390</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>79</v>
@@ -11438,21 +11401,21 @@
         <v>81</v>
       </c>
       <c r="AM68" t="s" s="2">
-        <v>396</v>
+        <v>391</v>
       </c>
       <c r="AN68" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AO68" t="s" s="2">
-        <v>397</v>
+        <v>392</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="s" s="2">
-        <v>398</v>
+        <v>393</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>399</v>
+        <v>394</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -11478,13 +11441,13 @@
         <v>104</v>
       </c>
       <c r="L69" t="s" s="2">
-        <v>400</v>
+        <v>395</v>
       </c>
       <c r="M69" t="s" s="2">
-        <v>401</v>
+        <v>396</v>
       </c>
       <c r="N69" t="s" s="2">
-        <v>402</v>
+        <v>397</v>
       </c>
       <c r="O69" s="2"/>
       <c r="P69" t="s" s="2">
@@ -11498,7 +11461,7 @@
         <v>81</v>
       </c>
       <c r="T69" t="s" s="2">
-        <v>403</v>
+        <v>398</v>
       </c>
       <c r="U69" t="s" s="2">
         <v>81</v>
@@ -11534,7 +11497,7 @@
         <v>81</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>404</v>
+        <v>399</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>79</v>
@@ -11555,21 +11518,21 @@
         <v>81</v>
       </c>
       <c r="AM69" t="s" s="2">
-        <v>405</v>
+        <v>400</v>
       </c>
       <c r="AN69" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AO69" t="s" s="2">
-        <v>406</v>
+        <v>401</v>
       </c>
     </row>
     <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
-        <v>407</v>
+        <v>402</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>408</v>
+        <v>403</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -11592,17 +11555,15 @@
         <v>91</v>
       </c>
       <c r="K70" t="s" s="2">
-        <v>334</v>
+        <v>329</v>
       </c>
       <c r="L70" t="s" s="2">
-        <v>409</v>
+        <v>404</v>
       </c>
       <c r="M70" t="s" s="2">
-        <v>410</v>
-      </c>
-      <c r="N70" t="s" s="2">
-        <v>411</v>
-      </c>
+        <v>405</v>
+      </c>
+      <c r="N70" s="2"/>
       <c r="O70" s="2"/>
       <c r="P70" t="s" s="2">
         <v>81</v>
@@ -11651,7 +11612,7 @@
         <v>81</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>412</v>
+        <v>406</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>79</v>
@@ -11660,10 +11621,10 @@
         <v>90</v>
       </c>
       <c r="AI70" t="s" s="2">
-        <v>152</v>
+        <v>81</v>
       </c>
       <c r="AJ70" t="s" s="2">
-        <v>413</v>
+        <v>102</v>
       </c>
       <c r="AK70" t="s" s="2">
         <v>81</v>
@@ -11672,21 +11633,21 @@
         <v>81</v>
       </c>
       <c r="AM70" t="s" s="2">
-        <v>414</v>
+        <v>407</v>
       </c>
       <c r="AN70" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AO70" t="s" s="2">
-        <v>415</v>
+        <v>408</v>
       </c>
     </row>
     <row r="71" hidden="true">
       <c r="A71" t="s" s="2">
-        <v>416</v>
+        <v>409</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>417</v>
+        <v>410</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -11709,16 +11670,16 @@
         <v>91</v>
       </c>
       <c r="K71" t="s" s="2">
-        <v>418</v>
+        <v>411</v>
       </c>
       <c r="L71" t="s" s="2">
-        <v>419</v>
+        <v>412</v>
       </c>
       <c r="M71" t="s" s="2">
-        <v>420</v>
+        <v>413</v>
       </c>
       <c r="N71" t="s" s="2">
-        <v>421</v>
+        <v>414</v>
       </c>
       <c r="O71" s="2"/>
       <c r="P71" t="s" s="2">
@@ -11768,7 +11729,7 @@
         <v>81</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>422</v>
+        <v>415</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>79</v>
@@ -11777,10 +11738,10 @@
         <v>90</v>
       </c>
       <c r="AI71" t="s" s="2">
-        <v>152</v>
+        <v>81</v>
       </c>
       <c r="AJ71" t="s" s="2">
-        <v>423</v>
+        <v>102</v>
       </c>
       <c r="AK71" t="s" s="2">
         <v>81</v>
@@ -11789,21 +11750,21 @@
         <v>81</v>
       </c>
       <c r="AM71" t="s" s="2">
-        <v>424</v>
+        <v>416</v>
       </c>
       <c r="AN71" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AO71" t="s" s="2">
-        <v>425</v>
+        <v>417</v>
       </c>
     </row>
     <row r="72" hidden="true">
       <c r="A72" t="s" s="2">
-        <v>426</v>
+        <v>418</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>427</v>
+        <v>419</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -11843,7 +11804,7 @@
       </c>
       <c r="Q72" s="2"/>
       <c r="R72" t="s" s="2">
-        <v>428</v>
+        <v>420</v>
       </c>
       <c r="S72" t="s" s="2">
         <v>81</v>
@@ -11917,10 +11878,10 @@
     </row>
     <row r="73" hidden="true">
       <c r="A73" t="s" s="2">
-        <v>429</v>
+        <v>421</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>430</v>
+        <v>422</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -11943,7 +11904,7 @@
         <v>81</v>
       </c>
       <c r="K73" t="s" s="2">
-        <v>431</v>
+        <v>423</v>
       </c>
       <c r="L73" t="s" s="2">
         <v>237</v>
@@ -12009,7 +11970,7 @@
         <v>90</v>
       </c>
       <c r="AI73" t="s" s="2">
-        <v>152</v>
+        <v>81</v>
       </c>
       <c r="AJ73" t="s" s="2">
         <v>102</v>
@@ -12032,13 +11993,13 @@
     </row>
     <row r="74">
       <c r="A74" t="s" s="2">
-        <v>432</v>
+        <v>424</v>
       </c>
       <c r="B74" t="s" s="2">
         <v>193</v>
       </c>
       <c r="C74" t="s" s="2">
-        <v>433</v>
+        <v>425</v>
       </c>
       <c r="D74" t="s" s="2">
         <v>110</v>
@@ -12060,13 +12021,13 @@
         <v>81</v>
       </c>
       <c r="K74" t="s" s="2">
-        <v>434</v>
+        <v>426</v>
       </c>
       <c r="L74" t="s" s="2">
-        <v>200</v>
+        <v>194</v>
       </c>
       <c r="M74" t="s" s="2">
-        <v>435</v>
+        <v>427</v>
       </c>
       <c r="N74" t="s" s="2">
         <v>114</v>
@@ -12140,7 +12101,7 @@
         <v>81</v>
       </c>
       <c r="AM74" t="s" s="2">
-        <v>108</v>
+        <v>192</v>
       </c>
       <c r="AN74" t="s" s="2">
         <v>81</v>
@@ -12151,13 +12112,13 @@
     </row>
     <row r="75">
       <c r="A75" t="s" s="2">
-        <v>436</v>
+        <v>428</v>
       </c>
       <c r="B75" t="s" s="2">
         <v>193</v>
       </c>
       <c r="C75" t="s" s="2">
-        <v>437</v>
+        <v>429</v>
       </c>
       <c r="D75" t="s" s="2">
         <v>110</v>
@@ -12179,13 +12140,13 @@
         <v>81</v>
       </c>
       <c r="K75" t="s" s="2">
-        <v>438</v>
+        <v>430</v>
       </c>
       <c r="L75" t="s" s="2">
         <v>200</v>
       </c>
       <c r="M75" t="s" s="2">
-        <v>439</v>
+        <v>431</v>
       </c>
       <c r="N75" t="s" s="2">
         <v>114</v>
@@ -12270,13 +12231,13 @@
     </row>
     <row r="76">
       <c r="A76" t="s" s="2">
-        <v>440</v>
+        <v>432</v>
       </c>
       <c r="B76" t="s" s="2">
         <v>193</v>
       </c>
       <c r="C76" t="s" s="2">
-        <v>441</v>
+        <v>433</v>
       </c>
       <c r="D76" t="s" s="2">
         <v>110</v>
@@ -12298,13 +12259,13 @@
         <v>81</v>
       </c>
       <c r="K76" t="s" s="2">
-        <v>442</v>
+        <v>434</v>
       </c>
       <c r="L76" t="s" s="2">
-        <v>200</v>
+        <v>194</v>
       </c>
       <c r="M76" t="s" s="2">
-        <v>443</v>
+        <v>435</v>
       </c>
       <c r="N76" t="s" s="2">
         <v>114</v>
@@ -12378,7 +12339,7 @@
         <v>81</v>
       </c>
       <c r="AM76" t="s" s="2">
-        <v>108</v>
+        <v>192</v>
       </c>
       <c r="AN76" t="s" s="2">
         <v>81</v>
@@ -12389,7 +12350,7 @@
     </row>
     <row r="77" hidden="true">
       <c r="A77" t="s" s="2">
-        <v>444</v>
+        <v>436</v>
       </c>
       <c r="B77" t="s" s="2">
         <v>208</v>
@@ -12504,14 +12465,14 @@
     </row>
     <row r="78" hidden="true">
       <c r="A78" t="s" s="2">
-        <v>445</v>
+        <v>437</v>
       </c>
       <c r="B78" t="s" s="2">
         <v>210</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
-        <v>110</v>
+        <v>81</v>
       </c>
       <c r="E78" s="2"/>
       <c r="F78" t="s" s="2">
@@ -12533,14 +12494,12 @@
         <v>111</v>
       </c>
       <c r="L78" t="s" s="2">
-        <v>112</v>
+        <v>194</v>
       </c>
       <c r="M78" t="s" s="2">
-        <v>113</v>
-      </c>
-      <c r="N78" t="s" s="2">
-        <v>114</v>
-      </c>
+        <v>195</v>
+      </c>
+      <c r="N78" s="2"/>
       <c r="O78" s="2"/>
       <c r="P78" t="s" s="2">
         <v>81</v>
@@ -12610,7 +12569,7 @@
         <v>81</v>
       </c>
       <c r="AM78" t="s" s="2">
-        <v>108</v>
+        <v>81</v>
       </c>
       <c r="AN78" t="s" s="2">
         <v>81</v>
@@ -12621,10 +12580,10 @@
     </row>
     <row r="79" hidden="true">
       <c r="A79" t="s" s="2">
-        <v>446</v>
+        <v>438</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>427</v>
+        <v>419</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
@@ -12664,7 +12623,7 @@
       </c>
       <c r="Q79" s="2"/>
       <c r="R79" t="s" s="2">
-        <v>447</v>
+        <v>439</v>
       </c>
       <c r="S79" t="s" s="2">
         <v>81</v>
@@ -12738,10 +12697,10 @@
     </row>
     <row r="80">
       <c r="A80" t="s" s="2">
-        <v>448</v>
+        <v>440</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>430</v>
+        <v>422</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
@@ -12764,7 +12723,7 @@
         <v>81</v>
       </c>
       <c r="K80" t="s" s="2">
-        <v>363</v>
+        <v>358</v>
       </c>
       <c r="L80" t="s" s="2">
         <v>237</v>
@@ -12830,7 +12789,7 @@
         <v>90</v>
       </c>
       <c r="AI80" t="s" s="2">
-        <v>152</v>
+        <v>81</v>
       </c>
       <c r="AJ80" t="s" s="2">
         <v>102</v>
@@ -12853,10 +12812,10 @@
     </row>
     <row r="81" hidden="true">
       <c r="A81" t="s" s="2">
-        <v>449</v>
+        <v>441</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>450</v>
+        <v>442</v>
       </c>
       <c r="C81" s="2"/>
       <c r="D81" t="s" s="2">
@@ -12968,10 +12927,10 @@
     </row>
     <row r="82" hidden="true">
       <c r="A82" t="s" s="2">
-        <v>451</v>
+        <v>443</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>452</v>
+        <v>444</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" t="s" s="2">
@@ -13085,10 +13044,10 @@
     </row>
     <row r="83" hidden="true">
       <c r="A83" t="s" s="2">
-        <v>453</v>
+        <v>445</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>454</v>
+        <v>446</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" t="s" s="2">
@@ -13114,16 +13073,16 @@
         <v>169</v>
       </c>
       <c r="L83" t="s" s="2">
-        <v>368</v>
+        <v>363</v>
       </c>
       <c r="M83" t="s" s="2">
-        <v>369</v>
+        <v>364</v>
       </c>
       <c r="N83" t="s" s="2">
-        <v>370</v>
+        <v>365</v>
       </c>
       <c r="O83" t="s" s="2">
-        <v>371</v>
+        <v>366</v>
       </c>
       <c r="P83" t="s" s="2">
         <v>81</v>
@@ -13148,13 +13107,13 @@
         <v>81</v>
       </c>
       <c r="X83" t="s" s="2">
-        <v>273</v>
+        <v>270</v>
       </c>
       <c r="Y83" t="s" s="2">
-        <v>372</v>
+        <v>367</v>
       </c>
       <c r="Z83" t="s" s="2">
-        <v>373</v>
+        <v>368</v>
       </c>
       <c r="AA83" t="s" s="2">
         <v>81</v>
@@ -13172,7 +13131,7 @@
         <v>81</v>
       </c>
       <c r="AF83" t="s" s="2">
-        <v>374</v>
+        <v>369</v>
       </c>
       <c r="AG83" t="s" s="2">
         <v>79</v>
@@ -13193,7 +13152,7 @@
         <v>81</v>
       </c>
       <c r="AM83" t="s" s="2">
-        <v>375</v>
+        <v>370</v>
       </c>
       <c r="AN83" t="s" s="2">
         <v>81</v>
@@ -13204,10 +13163,10 @@
     </row>
     <row r="84" hidden="true">
       <c r="A84" t="s" s="2">
-        <v>455</v>
+        <v>447</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>456</v>
+        <v>448</v>
       </c>
       <c r="C84" s="2"/>
       <c r="D84" t="s" s="2">
@@ -13230,19 +13189,19 @@
         <v>91</v>
       </c>
       <c r="K84" t="s" s="2">
-        <v>378</v>
+        <v>373</v>
       </c>
       <c r="L84" t="s" s="2">
-        <v>379</v>
+        <v>374</v>
       </c>
       <c r="M84" t="s" s="2">
-        <v>380</v>
+        <v>375</v>
       </c>
       <c r="N84" t="s" s="2">
-        <v>381</v>
+        <v>376</v>
       </c>
       <c r="O84" t="s" s="2">
-        <v>382</v>
+        <v>377</v>
       </c>
       <c r="P84" t="s" s="2">
         <v>81</v>
@@ -13270,10 +13229,10 @@
         <v>148</v>
       </c>
       <c r="Y84" t="s" s="2">
-        <v>383</v>
+        <v>378</v>
       </c>
       <c r="Z84" t="s" s="2">
-        <v>384</v>
+        <v>379</v>
       </c>
       <c r="AA84" t="s" s="2">
         <v>81</v>
@@ -13291,7 +13250,7 @@
         <v>81</v>
       </c>
       <c r="AF84" t="s" s="2">
-        <v>385</v>
+        <v>380</v>
       </c>
       <c r="AG84" t="s" s="2">
         <v>79</v>
@@ -13300,7 +13259,7 @@
         <v>90</v>
       </c>
       <c r="AI84" t="s" s="2">
-        <v>152</v>
+        <v>81</v>
       </c>
       <c r="AJ84" t="s" s="2">
         <v>102</v>
@@ -13312,21 +13271,21 @@
         <v>81</v>
       </c>
       <c r="AM84" t="s" s="2">
-        <v>375</v>
+        <v>370</v>
       </c>
       <c r="AN84" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AO84" t="s" s="2">
-        <v>386</v>
+        <v>381</v>
       </c>
     </row>
     <row r="85" hidden="true">
       <c r="A85" t="s" s="2">
-        <v>457</v>
+        <v>449</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>458</v>
+        <v>450</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" t="s" s="2">
@@ -13352,16 +13311,16 @@
         <v>132</v>
       </c>
       <c r="L85" t="s" s="2">
-        <v>459</v>
+        <v>451</v>
       </c>
       <c r="M85" t="s" s="2">
-        <v>390</v>
+        <v>385</v>
       </c>
       <c r="N85" t="s" s="2">
-        <v>391</v>
+        <v>386</v>
       </c>
       <c r="O85" t="s" s="2">
-        <v>392</v>
+        <v>387</v>
       </c>
       <c r="P85" t="s" s="2">
         <v>81</v>
@@ -13374,7 +13333,7 @@
         <v>81</v>
       </c>
       <c r="T85" t="s" s="2">
-        <v>394</v>
+        <v>389</v>
       </c>
       <c r="U85" t="s" s="2">
         <v>81</v>
@@ -13410,7 +13369,7 @@
         <v>81</v>
       </c>
       <c r="AF85" t="s" s="2">
-        <v>395</v>
+        <v>390</v>
       </c>
       <c r="AG85" t="s" s="2">
         <v>79</v>
@@ -13431,21 +13390,21 @@
         <v>81</v>
       </c>
       <c r="AM85" t="s" s="2">
-        <v>396</v>
+        <v>391</v>
       </c>
       <c r="AN85" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AO85" t="s" s="2">
-        <v>397</v>
+        <v>392</v>
       </c>
     </row>
     <row r="86" hidden="true">
       <c r="A86" t="s" s="2">
-        <v>460</v>
+        <v>452</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>461</v>
+        <v>453</v>
       </c>
       <c r="C86" s="2"/>
       <c r="D86" t="s" s="2">
@@ -13471,13 +13430,13 @@
         <v>104</v>
       </c>
       <c r="L86" t="s" s="2">
-        <v>462</v>
+        <v>454</v>
       </c>
       <c r="M86" t="s" s="2">
-        <v>443</v>
+        <v>435</v>
       </c>
       <c r="N86" t="s" s="2">
-        <v>402</v>
+        <v>397</v>
       </c>
       <c r="O86" s="2"/>
       <c r="P86" t="s" s="2">
@@ -13491,7 +13450,7 @@
         <v>81</v>
       </c>
       <c r="T86" t="s" s="2">
-        <v>403</v>
+        <v>398</v>
       </c>
       <c r="U86" t="s" s="2">
         <v>81</v>
@@ -13527,7 +13486,7 @@
         <v>81</v>
       </c>
       <c r="AF86" t="s" s="2">
-        <v>404</v>
+        <v>399</v>
       </c>
       <c r="AG86" t="s" s="2">
         <v>79</v>
@@ -13548,21 +13507,21 @@
         <v>81</v>
       </c>
       <c r="AM86" t="s" s="2">
-        <v>405</v>
+        <v>400</v>
       </c>
       <c r="AN86" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AO86" t="s" s="2">
-        <v>406</v>
+        <v>401</v>
       </c>
     </row>
     <row r="87" hidden="true">
       <c r="A87" t="s" s="2">
-        <v>463</v>
+        <v>455</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>464</v>
+        <v>456</v>
       </c>
       <c r="C87" s="2"/>
       <c r="D87" t="s" s="2">
@@ -13585,17 +13544,15 @@
         <v>91</v>
       </c>
       <c r="K87" t="s" s="2">
-        <v>334</v>
+        <v>329</v>
       </c>
       <c r="L87" t="s" s="2">
-        <v>409</v>
+        <v>404</v>
       </c>
       <c r="M87" t="s" s="2">
-        <v>410</v>
-      </c>
-      <c r="N87" t="s" s="2">
-        <v>411</v>
-      </c>
+        <v>405</v>
+      </c>
+      <c r="N87" s="2"/>
       <c r="O87" s="2"/>
       <c r="P87" t="s" s="2">
         <v>81</v>
@@ -13644,7 +13601,7 @@
         <v>81</v>
       </c>
       <c r="AF87" t="s" s="2">
-        <v>412</v>
+        <v>406</v>
       </c>
       <c r="AG87" t="s" s="2">
         <v>79</v>
@@ -13653,10 +13610,10 @@
         <v>90</v>
       </c>
       <c r="AI87" t="s" s="2">
-        <v>152</v>
+        <v>81</v>
       </c>
       <c r="AJ87" t="s" s="2">
-        <v>413</v>
+        <v>102</v>
       </c>
       <c r="AK87" t="s" s="2">
         <v>81</v>
@@ -13665,21 +13622,21 @@
         <v>81</v>
       </c>
       <c r="AM87" t="s" s="2">
-        <v>414</v>
+        <v>407</v>
       </c>
       <c r="AN87" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AO87" t="s" s="2">
-        <v>415</v>
+        <v>408</v>
       </c>
     </row>
     <row r="88" hidden="true">
       <c r="A88" t="s" s="2">
-        <v>465</v>
+        <v>457</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>466</v>
+        <v>458</v>
       </c>
       <c r="C88" s="2"/>
       <c r="D88" t="s" s="2">
@@ -13702,16 +13659,16 @@
         <v>91</v>
       </c>
       <c r="K88" t="s" s="2">
-        <v>418</v>
+        <v>411</v>
       </c>
       <c r="L88" t="s" s="2">
-        <v>419</v>
+        <v>412</v>
       </c>
       <c r="M88" t="s" s="2">
-        <v>420</v>
+        <v>413</v>
       </c>
       <c r="N88" t="s" s="2">
-        <v>421</v>
+        <v>414</v>
       </c>
       <c r="O88" s="2"/>
       <c r="P88" t="s" s="2">
@@ -13761,7 +13718,7 @@
         <v>81</v>
       </c>
       <c r="AF88" t="s" s="2">
-        <v>422</v>
+        <v>415</v>
       </c>
       <c r="AG88" t="s" s="2">
         <v>79</v>
@@ -13770,10 +13727,10 @@
         <v>90</v>
       </c>
       <c r="AI88" t="s" s="2">
-        <v>152</v>
+        <v>81</v>
       </c>
       <c r="AJ88" t="s" s="2">
-        <v>423</v>
+        <v>102</v>
       </c>
       <c r="AK88" t="s" s="2">
         <v>81</v>
@@ -13782,24 +13739,24 @@
         <v>81</v>
       </c>
       <c r="AM88" t="s" s="2">
-        <v>424</v>
+        <v>416</v>
       </c>
       <c r="AN88" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AO88" t="s" s="2">
-        <v>425</v>
+        <v>417</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="s" s="2">
-        <v>467</v>
+        <v>459</v>
       </c>
       <c r="B89" t="s" s="2">
         <v>193</v>
       </c>
       <c r="C89" t="s" s="2">
-        <v>468</v>
+        <v>460</v>
       </c>
       <c r="D89" t="s" s="2">
         <v>110</v>
@@ -13821,13 +13778,13 @@
         <v>81</v>
       </c>
       <c r="K89" t="s" s="2">
-        <v>469</v>
+        <v>461</v>
       </c>
       <c r="L89" t="s" s="2">
         <v>194</v>
       </c>
       <c r="M89" t="s" s="2">
-        <v>470</v>
+        <v>462</v>
       </c>
       <c r="N89" t="s" s="2">
         <v>114</v>
@@ -13912,13 +13869,13 @@
     </row>
     <row r="90">
       <c r="A90" t="s" s="2">
-        <v>471</v>
+        <v>463</v>
       </c>
       <c r="B90" t="s" s="2">
         <v>193</v>
       </c>
       <c r="C90" t="s" s="2">
-        <v>472</v>
+        <v>464</v>
       </c>
       <c r="D90" t="s" s="2">
         <v>110</v>
@@ -13940,13 +13897,13 @@
         <v>81</v>
       </c>
       <c r="K90" t="s" s="2">
-        <v>473</v>
+        <v>465</v>
       </c>
       <c r="L90" t="s" s="2">
-        <v>474</v>
+        <v>466</v>
       </c>
       <c r="M90" t="s" s="2">
-        <v>475</v>
+        <v>467</v>
       </c>
       <c r="N90" t="s" s="2">
         <v>114</v>
@@ -14020,7 +13977,7 @@
         <v>81</v>
       </c>
       <c r="AM90" t="s" s="2">
-        <v>108</v>
+        <v>192</v>
       </c>
       <c r="AN90" t="s" s="2">
         <v>81</v>
@@ -14031,7 +13988,7 @@
     </row>
     <row r="91" hidden="true">
       <c r="A91" t="s" s="2">
-        <v>476</v>
+        <v>468</v>
       </c>
       <c r="B91" t="s" s="2">
         <v>208</v>
@@ -14146,14 +14103,14 @@
     </row>
     <row r="92" hidden="true">
       <c r="A92" t="s" s="2">
-        <v>477</v>
+        <v>469</v>
       </c>
       <c r="B92" t="s" s="2">
         <v>210</v>
       </c>
       <c r="C92" s="2"/>
       <c r="D92" t="s" s="2">
-        <v>110</v>
+        <v>81</v>
       </c>
       <c r="E92" s="2"/>
       <c r="F92" t="s" s="2">
@@ -14175,14 +14132,12 @@
         <v>111</v>
       </c>
       <c r="L92" t="s" s="2">
-        <v>112</v>
+        <v>194</v>
       </c>
       <c r="M92" t="s" s="2">
-        <v>113</v>
-      </c>
-      <c r="N92" t="s" s="2">
-        <v>114</v>
-      </c>
+        <v>195</v>
+      </c>
+      <c r="N92" s="2"/>
       <c r="O92" s="2"/>
       <c r="P92" t="s" s="2">
         <v>81</v>
@@ -14252,7 +14207,7 @@
         <v>81</v>
       </c>
       <c r="AM92" t="s" s="2">
-        <v>108</v>
+        <v>81</v>
       </c>
       <c r="AN92" t="s" s="2">
         <v>81</v>
@@ -14263,16 +14218,16 @@
     </row>
     <row r="93">
       <c r="A93" t="s" s="2">
-        <v>478</v>
+        <v>470</v>
       </c>
       <c r="B93" t="s" s="2">
         <v>210</v>
       </c>
       <c r="C93" t="s" s="2">
-        <v>479</v>
+        <v>471</v>
       </c>
       <c r="D93" t="s" s="2">
-        <v>110</v>
+        <v>81</v>
       </c>
       <c r="E93" s="2"/>
       <c r="F93" t="s" s="2">
@@ -14294,14 +14249,12 @@
         <v>111</v>
       </c>
       <c r="L93" t="s" s="2">
-        <v>112</v>
+        <v>194</v>
       </c>
       <c r="M93" t="s" s="2">
-        <v>113</v>
-      </c>
-      <c r="N93" t="s" s="2">
-        <v>114</v>
-      </c>
+        <v>195</v>
+      </c>
+      <c r="N93" s="2"/>
       <c r="O93" s="2"/>
       <c r="P93" t="s" s="2">
         <v>81</v>
@@ -14371,7 +14324,7 @@
         <v>81</v>
       </c>
       <c r="AM93" t="s" s="2">
-        <v>108</v>
+        <v>81</v>
       </c>
       <c r="AN93" t="s" s="2">
         <v>81</v>
@@ -14382,7 +14335,7 @@
     </row>
     <row r="94" hidden="true">
       <c r="A94" t="s" s="2">
-        <v>480</v>
+        <v>472</v>
       </c>
       <c r="B94" t="s" s="2">
         <v>215</v>
@@ -14497,14 +14450,14 @@
     </row>
     <row r="95" hidden="true">
       <c r="A95" t="s" s="2">
-        <v>481</v>
+        <v>473</v>
       </c>
       <c r="B95" t="s" s="2">
         <v>217</v>
       </c>
       <c r="C95" s="2"/>
       <c r="D95" t="s" s="2">
-        <v>110</v>
+        <v>81</v>
       </c>
       <c r="E95" s="2"/>
       <c r="F95" t="s" s="2">
@@ -14526,14 +14479,12 @@
         <v>111</v>
       </c>
       <c r="L95" t="s" s="2">
-        <v>112</v>
+        <v>194</v>
       </c>
       <c r="M95" t="s" s="2">
-        <v>113</v>
-      </c>
-      <c r="N95" t="s" s="2">
-        <v>114</v>
-      </c>
+        <v>195</v>
+      </c>
+      <c r="N95" s="2"/>
       <c r="O95" s="2"/>
       <c r="P95" t="s" s="2">
         <v>81</v>
@@ -14603,7 +14554,7 @@
         <v>81</v>
       </c>
       <c r="AM95" t="s" s="2">
-        <v>108</v>
+        <v>81</v>
       </c>
       <c r="AN95" t="s" s="2">
         <v>81</v>
@@ -14614,7 +14565,7 @@
     </row>
     <row r="96" hidden="true">
       <c r="A96" t="s" s="2">
-        <v>482</v>
+        <v>474</v>
       </c>
       <c r="B96" t="s" s="2">
         <v>219</v>
@@ -14657,7 +14608,7 @@
       </c>
       <c r="Q96" s="2"/>
       <c r="R96" t="s" s="2">
-        <v>479</v>
+        <v>471</v>
       </c>
       <c r="S96" t="s" s="2">
         <v>81</v>
@@ -14731,7 +14682,7 @@
     </row>
     <row r="97">
       <c r="A97" t="s" s="2">
-        <v>483</v>
+        <v>475</v>
       </c>
       <c r="B97" t="s" s="2">
         <v>225</v>
@@ -14766,7 +14717,7 @@
         <v>238</v>
       </c>
       <c r="N97" t="s" s="2">
-        <v>484</v>
+        <v>476</v>
       </c>
       <c r="O97" s="2"/>
       <c r="P97" t="s" s="2">
@@ -14777,7 +14728,7 @@
         <v>81</v>
       </c>
       <c r="S97" t="s" s="2">
-        <v>485</v>
+        <v>477</v>
       </c>
       <c r="T97" t="s" s="2">
         <v>81</v>
@@ -14792,11 +14743,11 @@
         <v>81</v>
       </c>
       <c r="X97" t="s" s="2">
-        <v>273</v>
+        <v>270</v>
       </c>
       <c r="Y97" s="2"/>
       <c r="Z97" t="s" s="2">
-        <v>486</v>
+        <v>478</v>
       </c>
       <c r="AA97" t="s" s="2">
         <v>81</v>
@@ -14823,7 +14774,7 @@
         <v>90</v>
       </c>
       <c r="AI97" t="s" s="2">
-        <v>152</v>
+        <v>81</v>
       </c>
       <c r="AJ97" t="s" s="2">
         <v>102</v>
@@ -14846,7 +14797,7 @@
     </row>
     <row r="98" hidden="true">
       <c r="A98" t="s" s="2">
-        <v>487</v>
+        <v>479</v>
       </c>
       <c r="B98" t="s" s="2">
         <v>240</v>
@@ -14961,7 +14912,7 @@
     </row>
     <row r="99" hidden="true">
       <c r="A99" t="s" s="2">
-        <v>488</v>
+        <v>480</v>
       </c>
       <c r="B99" t="s" s="2">
         <v>242</v>
@@ -15078,10 +15029,10 @@
     </row>
     <row r="100">
       <c r="A100" t="s" s="2">
-        <v>489</v>
+        <v>481</v>
       </c>
       <c r="B100" t="s" s="2">
-        <v>388</v>
+        <v>383</v>
       </c>
       <c r="C100" s="2"/>
       <c r="D100" t="s" s="2">
@@ -15107,16 +15058,16 @@
         <v>132</v>
       </c>
       <c r="L100" t="s" s="2">
-        <v>490</v>
+        <v>482</v>
       </c>
       <c r="M100" t="s" s="2">
-        <v>491</v>
+        <v>483</v>
       </c>
       <c r="N100" t="s" s="2">
-        <v>492</v>
+        <v>484</v>
       </c>
       <c r="O100" t="s" s="2">
-        <v>493</v>
+        <v>485</v>
       </c>
       <c r="P100" t="s" s="2">
         <v>81</v>
@@ -15165,7 +15116,7 @@
         <v>81</v>
       </c>
       <c r="AF100" t="s" s="2">
-        <v>494</v>
+        <v>486</v>
       </c>
       <c r="AG100" t="s" s="2">
         <v>79</v>
@@ -15186,21 +15137,21 @@
         <v>81</v>
       </c>
       <c r="AM100" t="s" s="2">
-        <v>495</v>
+        <v>487</v>
       </c>
       <c r="AN100" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AO100" t="s" s="2">
-        <v>496</v>
+        <v>488</v>
       </c>
     </row>
     <row r="101" hidden="true">
       <c r="A101" t="s" s="2">
-        <v>497</v>
+        <v>489</v>
       </c>
       <c r="B101" t="s" s="2">
-        <v>498</v>
+        <v>490</v>
       </c>
       <c r="C101" s="2"/>
       <c r="D101" t="s" s="2">
@@ -15226,13 +15177,13 @@
         <v>104</v>
       </c>
       <c r="L101" t="s" s="2">
-        <v>499</v>
+        <v>491</v>
       </c>
       <c r="M101" t="s" s="2">
-        <v>500</v>
+        <v>492</v>
       </c>
       <c r="N101" t="s" s="2">
-        <v>501</v>
+        <v>493</v>
       </c>
       <c r="O101" s="2"/>
       <c r="P101" t="s" s="2">
@@ -15282,7 +15233,7 @@
         <v>81</v>
       </c>
       <c r="AF101" t="s" s="2">
-        <v>502</v>
+        <v>494</v>
       </c>
       <c r="AG101" t="s" s="2">
         <v>79</v>
@@ -15303,21 +15254,21 @@
         <v>81</v>
       </c>
       <c r="AM101" t="s" s="2">
-        <v>503</v>
+        <v>495</v>
       </c>
       <c r="AN101" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AO101" t="s" s="2">
-        <v>504</v>
+        <v>496</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="s" s="2">
-        <v>505</v>
+        <v>497</v>
       </c>
       <c r="B102" t="s" s="2">
-        <v>506</v>
+        <v>498</v>
       </c>
       <c r="C102" s="2"/>
       <c r="D102" t="s" s="2">
@@ -15343,14 +15294,14 @@
         <v>169</v>
       </c>
       <c r="L102" t="s" s="2">
-        <v>507</v>
+        <v>499</v>
       </c>
       <c r="M102" t="s" s="2">
-        <v>507</v>
+        <v>499</v>
       </c>
       <c r="N102" s="2"/>
       <c r="O102" t="s" s="2">
-        <v>508</v>
+        <v>500</v>
       </c>
       <c r="P102" t="s" s="2">
         <v>81</v>
@@ -15399,7 +15350,7 @@
         <v>81</v>
       </c>
       <c r="AF102" t="s" s="2">
-        <v>509</v>
+        <v>501</v>
       </c>
       <c r="AG102" t="s" s="2">
         <v>79</v>
@@ -15420,21 +15371,21 @@
         <v>81</v>
       </c>
       <c r="AM102" t="s" s="2">
-        <v>510</v>
+        <v>502</v>
       </c>
       <c r="AN102" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AO102" t="s" s="2">
-        <v>511</v>
+        <v>503</v>
       </c>
     </row>
     <row r="103" hidden="true">
       <c r="A103" t="s" s="2">
-        <v>512</v>
+        <v>504</v>
       </c>
       <c r="B103" t="s" s="2">
-        <v>513</v>
+        <v>505</v>
       </c>
       <c r="C103" s="2"/>
       <c r="D103" t="s" s="2">
@@ -15460,16 +15411,14 @@
         <v>104</v>
       </c>
       <c r="L103" t="s" s="2">
-        <v>514</v>
+        <v>506</v>
       </c>
       <c r="M103" t="s" s="2">
-        <v>515</v>
-      </c>
-      <c r="N103" t="s" s="2">
-        <v>283</v>
-      </c>
+        <v>507</v>
+      </c>
+      <c r="N103" s="2"/>
       <c r="O103" t="s" s="2">
-        <v>516</v>
+        <v>508</v>
       </c>
       <c r="P103" t="s" s="2">
         <v>81</v>
@@ -15518,7 +15467,7 @@
         <v>81</v>
       </c>
       <c r="AF103" t="s" s="2">
-        <v>517</v>
+        <v>509</v>
       </c>
       <c r="AG103" t="s" s="2">
         <v>79</v>
@@ -15539,21 +15488,21 @@
         <v>81</v>
       </c>
       <c r="AM103" t="s" s="2">
-        <v>518</v>
+        <v>510</v>
       </c>
       <c r="AN103" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AO103" t="s" s="2">
-        <v>519</v>
+        <v>511</v>
       </c>
     </row>
     <row r="104" hidden="true">
       <c r="A104" t="s" s="2">
-        <v>520</v>
+        <v>512</v>
       </c>
       <c r="B104" t="s" s="2">
-        <v>521</v>
+        <v>513</v>
       </c>
       <c r="C104" s="2"/>
       <c r="D104" t="s" s="2">
@@ -15579,16 +15528,16 @@
         <v>226</v>
       </c>
       <c r="L104" t="s" s="2">
-        <v>522</v>
+        <v>514</v>
       </c>
       <c r="M104" t="s" s="2">
-        <v>523</v>
+        <v>515</v>
       </c>
       <c r="N104" t="s" s="2">
-        <v>524</v>
+        <v>516</v>
       </c>
       <c r="O104" t="s" s="2">
-        <v>525</v>
+        <v>517</v>
       </c>
       <c r="P104" t="s" s="2">
         <v>81</v>
@@ -15637,7 +15586,7 @@
         <v>81</v>
       </c>
       <c r="AF104" t="s" s="2">
-        <v>526</v>
+        <v>518</v>
       </c>
       <c r="AG104" t="s" s="2">
         <v>79</v>
@@ -15658,27 +15607,27 @@
         <v>81</v>
       </c>
       <c r="AM104" t="s" s="2">
-        <v>527</v>
+        <v>519</v>
       </c>
       <c r="AN104" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AO104" t="s" s="2">
-        <v>528</v>
+        <v>520</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="s" s="2">
-        <v>529</v>
+        <v>521</v>
       </c>
       <c r="B105" t="s" s="2">
         <v>210</v>
       </c>
       <c r="C105" t="s" s="2">
-        <v>530</v>
+        <v>522</v>
       </c>
       <c r="D105" t="s" s="2">
-        <v>110</v>
+        <v>81</v>
       </c>
       <c r="E105" s="2"/>
       <c r="F105" t="s" s="2">
@@ -15700,14 +15649,12 @@
         <v>111</v>
       </c>
       <c r="L105" t="s" s="2">
-        <v>112</v>
+        <v>194</v>
       </c>
       <c r="M105" t="s" s="2">
-        <v>113</v>
-      </c>
-      <c r="N105" t="s" s="2">
-        <v>114</v>
-      </c>
+        <v>195</v>
+      </c>
+      <c r="N105" s="2"/>
       <c r="O105" s="2"/>
       <c r="P105" t="s" s="2">
         <v>81</v>
@@ -15777,7 +15724,7 @@
         <v>81</v>
       </c>
       <c r="AM105" t="s" s="2">
-        <v>108</v>
+        <v>81</v>
       </c>
       <c r="AN105" t="s" s="2">
         <v>81</v>
@@ -15788,7 +15735,7 @@
     </row>
     <row r="106" hidden="true">
       <c r="A106" t="s" s="2">
-        <v>531</v>
+        <v>523</v>
       </c>
       <c r="B106" t="s" s="2">
         <v>215</v>
@@ -15903,14 +15850,14 @@
     </row>
     <row r="107" hidden="true">
       <c r="A107" t="s" s="2">
-        <v>532</v>
+        <v>524</v>
       </c>
       <c r="B107" t="s" s="2">
         <v>217</v>
       </c>
       <c r="C107" s="2"/>
       <c r="D107" t="s" s="2">
-        <v>110</v>
+        <v>81</v>
       </c>
       <c r="E107" s="2"/>
       <c r="F107" t="s" s="2">
@@ -15932,14 +15879,12 @@
         <v>111</v>
       </c>
       <c r="L107" t="s" s="2">
-        <v>112</v>
+        <v>194</v>
       </c>
       <c r="M107" t="s" s="2">
-        <v>113</v>
-      </c>
-      <c r="N107" t="s" s="2">
-        <v>114</v>
-      </c>
+        <v>195</v>
+      </c>
+      <c r="N107" s="2"/>
       <c r="O107" s="2"/>
       <c r="P107" t="s" s="2">
         <v>81</v>
@@ -16009,7 +15954,7 @@
         <v>81</v>
       </c>
       <c r="AM107" t="s" s="2">
-        <v>108</v>
+        <v>81</v>
       </c>
       <c r="AN107" t="s" s="2">
         <v>81</v>
@@ -16020,7 +15965,7 @@
     </row>
     <row r="108" hidden="true">
       <c r="A108" t="s" s="2">
-        <v>533</v>
+        <v>525</v>
       </c>
       <c r="B108" t="s" s="2">
         <v>219</v>
@@ -16063,7 +16008,7 @@
       </c>
       <c r="Q108" s="2"/>
       <c r="R108" t="s" s="2">
-        <v>530</v>
+        <v>522</v>
       </c>
       <c r="S108" t="s" s="2">
         <v>81</v>
@@ -16137,7 +16082,7 @@
     </row>
     <row r="109">
       <c r="A109" t="s" s="2">
-        <v>534</v>
+        <v>526</v>
       </c>
       <c r="B109" t="s" s="2">
         <v>225</v>
@@ -16166,10 +16111,10 @@
         <v>104</v>
       </c>
       <c r="L109" t="s" s="2">
-        <v>535</v>
+        <v>527</v>
       </c>
       <c r="M109" t="s" s="2">
-        <v>536</v>
+        <v>528</v>
       </c>
       <c r="N109" s="2"/>
       <c r="O109" s="2"/>
@@ -16229,7 +16174,7 @@
         <v>90</v>
       </c>
       <c r="AI109" t="s" s="2">
-        <v>152</v>
+        <v>81</v>
       </c>
       <c r="AJ109" t="s" s="2">
         <v>102</v>
@@ -16252,10 +16197,10 @@
     </row>
     <row r="110" hidden="true">
       <c r="A110" t="s" s="2">
-        <v>537</v>
+        <v>529</v>
       </c>
       <c r="B110" t="s" s="2">
-        <v>427</v>
+        <v>419</v>
       </c>
       <c r="C110" s="2"/>
       <c r="D110" t="s" s="2">
@@ -16295,7 +16240,7 @@
       </c>
       <c r="Q110" s="2"/>
       <c r="R110" t="s" s="2">
-        <v>538</v>
+        <v>530</v>
       </c>
       <c r="S110" t="s" s="2">
         <v>81</v>
@@ -16369,10 +16314,10 @@
     </row>
     <row r="111" hidden="true">
       <c r="A111" t="s" s="2">
-        <v>539</v>
+        <v>531</v>
       </c>
       <c r="B111" t="s" s="2">
-        <v>430</v>
+        <v>422</v>
       </c>
       <c r="C111" s="2"/>
       <c r="D111" t="s" s="2">
@@ -16395,7 +16340,7 @@
         <v>81</v>
       </c>
       <c r="K111" t="s" s="2">
-        <v>431</v>
+        <v>423</v>
       </c>
       <c r="L111" t="s" s="2">
         <v>237</v>
@@ -16461,7 +16406,7 @@
         <v>90</v>
       </c>
       <c r="AI111" t="s" s="2">
-        <v>152</v>
+        <v>81</v>
       </c>
       <c r="AJ111" t="s" s="2">
         <v>102</v>
@@ -16484,13 +16429,13 @@
     </row>
     <row r="112">
       <c r="A112" t="s" s="2">
-        <v>540</v>
+        <v>532</v>
       </c>
       <c r="B112" t="s" s="2">
         <v>193</v>
       </c>
       <c r="C112" t="s" s="2">
-        <v>541</v>
+        <v>533</v>
       </c>
       <c r="D112" t="s" s="2">
         <v>110</v>
@@ -16512,13 +16457,13 @@
         <v>81</v>
       </c>
       <c r="K112" t="s" s="2">
-        <v>542</v>
+        <v>534</v>
       </c>
       <c r="L112" t="s" s="2">
-        <v>543</v>
+        <v>535</v>
       </c>
       <c r="M112" t="s" s="2">
-        <v>544</v>
+        <v>536</v>
       </c>
       <c r="N112" t="s" s="2">
         <v>114</v>
@@ -16592,7 +16537,7 @@
         <v>81</v>
       </c>
       <c r="AM112" t="s" s="2">
-        <v>108</v>
+        <v>192</v>
       </c>
       <c r="AN112" t="s" s="2">
         <v>81</v>
@@ -16603,13 +16548,13 @@
     </row>
     <row r="113">
       <c r="A113" t="s" s="2">
-        <v>545</v>
+        <v>537</v>
       </c>
       <c r="B113" t="s" s="2">
         <v>193</v>
       </c>
       <c r="C113" t="s" s="2">
-        <v>546</v>
+        <v>538</v>
       </c>
       <c r="D113" t="s" s="2">
         <v>110</v>
@@ -16631,16 +16576,16 @@
         <v>81</v>
       </c>
       <c r="K113" t="s" s="2">
-        <v>547</v>
+        <v>539</v>
       </c>
       <c r="L113" t="s" s="2">
-        <v>548</v>
+        <v>540</v>
       </c>
       <c r="M113" t="s" s="2">
-        <v>549</v>
+        <v>541</v>
       </c>
       <c r="N113" t="s" s="2">
-        <v>550</v>
+        <v>542</v>
       </c>
       <c r="O113" s="2"/>
       <c r="P113" t="s" s="2">
@@ -16722,7 +16667,7 @@
     </row>
     <row r="114" hidden="true">
       <c r="A114" t="s" s="2">
-        <v>551</v>
+        <v>543</v>
       </c>
       <c r="B114" t="s" s="2">
         <v>208</v>
@@ -16837,7 +16782,7 @@
     </row>
     <row r="115" hidden="true">
       <c r="A115" t="s" s="2">
-        <v>552</v>
+        <v>544</v>
       </c>
       <c r="B115" t="s" s="2">
         <v>210</v>
@@ -16954,10 +16899,10 @@
     </row>
     <row r="116" hidden="true">
       <c r="A116" t="s" s="2">
-        <v>553</v>
+        <v>545</v>
       </c>
       <c r="B116" t="s" s="2">
-        <v>427</v>
+        <v>419</v>
       </c>
       <c r="C116" s="2"/>
       <c r="D116" t="s" s="2">
@@ -16997,7 +16942,7 @@
       </c>
       <c r="Q116" s="2"/>
       <c r="R116" t="s" s="2">
-        <v>554</v>
+        <v>546</v>
       </c>
       <c r="S116" t="s" s="2">
         <v>81</v>
@@ -17071,10 +17016,10 @@
     </row>
     <row r="117">
       <c r="A117" t="s" s="2">
-        <v>555</v>
+        <v>547</v>
       </c>
       <c r="B117" t="s" s="2">
-        <v>430</v>
+        <v>422</v>
       </c>
       <c r="C117" s="2"/>
       <c r="D117" t="s" s="2">
@@ -17097,13 +17042,13 @@
         <v>81</v>
       </c>
       <c r="K117" t="s" s="2">
-        <v>556</v>
+        <v>548</v>
       </c>
       <c r="L117" t="s" s="2">
-        <v>557</v>
+        <v>549</v>
       </c>
       <c r="M117" t="s" s="2">
-        <v>558</v>
+        <v>550</v>
       </c>
       <c r="N117" s="2"/>
       <c r="O117" s="2"/>
@@ -17186,13 +17131,13 @@
     </row>
     <row r="118">
       <c r="A118" t="s" s="2">
-        <v>559</v>
+        <v>551</v>
       </c>
       <c r="B118" t="s" s="2">
         <v>193</v>
       </c>
       <c r="C118" t="s" s="2">
-        <v>560</v>
+        <v>552</v>
       </c>
       <c r="D118" t="s" s="2">
         <v>110</v>
@@ -17214,13 +17159,13 @@
         <v>81</v>
       </c>
       <c r="K118" t="s" s="2">
-        <v>561</v>
+        <v>553</v>
       </c>
       <c r="L118" t="s" s="2">
-        <v>562</v>
+        <v>554</v>
       </c>
       <c r="M118" t="s" s="2">
-        <v>563</v>
+        <v>555</v>
       </c>
       <c r="N118" t="s" s="2">
         <v>114</v>
@@ -17305,10 +17250,10 @@
     </row>
     <row r="119" hidden="true">
       <c r="A119" t="s" s="2">
-        <v>564</v>
+        <v>556</v>
       </c>
       <c r="B119" t="s" s="2">
-        <v>564</v>
+        <v>556</v>
       </c>
       <c r="C119" s="2"/>
       <c r="D119" t="s" s="2">
@@ -17334,16 +17279,16 @@
         <v>111</v>
       </c>
       <c r="L119" t="s" s="2">
-        <v>565</v>
+        <v>557</v>
       </c>
       <c r="M119" t="s" s="2">
-        <v>566</v>
+        <v>558</v>
       </c>
       <c r="N119" t="s" s="2">
         <v>114</v>
       </c>
       <c r="O119" t="s" s="2">
-        <v>567</v>
+        <v>559</v>
       </c>
       <c r="P119" t="s" s="2">
         <v>81</v>
@@ -17392,7 +17337,7 @@
         <v>117</v>
       </c>
       <c r="AF119" t="s" s="2">
-        <v>568</v>
+        <v>560</v>
       </c>
       <c r="AG119" t="s" s="2">
         <v>79</v>
@@ -17424,10 +17369,10 @@
     </row>
     <row r="120" hidden="true">
       <c r="A120" t="s" s="2">
-        <v>569</v>
+        <v>561</v>
       </c>
       <c r="B120" t="s" s="2">
-        <v>569</v>
+        <v>561</v>
       </c>
       <c r="C120" s="2"/>
       <c r="D120" t="s" s="2">
@@ -17450,16 +17395,16 @@
         <v>81</v>
       </c>
       <c r="K120" t="s" s="2">
-        <v>363</v>
+        <v>358</v>
       </c>
       <c r="L120" t="s" s="2">
-        <v>570</v>
+        <v>562</v>
       </c>
       <c r="M120" t="s" s="2">
-        <v>571</v>
+        <v>563</v>
       </c>
       <c r="N120" t="s" s="2">
-        <v>572</v>
+        <v>564</v>
       </c>
       <c r="O120" s="2"/>
       <c r="P120" t="s" s="2">
@@ -17497,10 +17442,10 @@
         <v>81</v>
       </c>
       <c r="AB120" t="s" s="2">
-        <v>573</v>
+        <v>565</v>
       </c>
       <c r="AC120" t="s" s="2">
-        <v>574</v>
+        <v>566</v>
       </c>
       <c r="AD120" t="s" s="2">
         <v>81</v>
@@ -17509,7 +17454,7 @@
         <v>117</v>
       </c>
       <c r="AF120" t="s" s="2">
-        <v>569</v>
+        <v>561</v>
       </c>
       <c r="AG120" t="s" s="2">
         <v>79</v>
@@ -17524,30 +17469,30 @@
         <v>102</v>
       </c>
       <c r="AK120" t="s" s="2">
-        <v>575</v>
+        <v>567</v>
       </c>
       <c r="AL120" t="s" s="2">
-        <v>576</v>
+        <v>568</v>
       </c>
       <c r="AM120" t="s" s="2">
-        <v>577</v>
+        <v>569</v>
       </c>
       <c r="AN120" t="s" s="2">
-        <v>578</v>
+        <v>570</v>
       </c>
       <c r="AO120" t="s" s="2">
-        <v>579</v>
+        <v>571</v>
       </c>
     </row>
     <row r="121" hidden="true">
       <c r="A121" t="s" s="2">
-        <v>580</v>
+        <v>572</v>
       </c>
       <c r="B121" t="s" s="2">
-        <v>569</v>
+        <v>561</v>
       </c>
       <c r="C121" t="s" s="2">
-        <v>581</v>
+        <v>573</v>
       </c>
       <c r="D121" t="s" s="2">
         <v>81</v>
@@ -17569,16 +17514,16 @@
         <v>81</v>
       </c>
       <c r="K121" t="s" s="2">
-        <v>582</v>
+        <v>574</v>
       </c>
       <c r="L121" t="s" s="2">
-        <v>583</v>
+        <v>575</v>
       </c>
       <c r="M121" t="s" s="2">
-        <v>584</v>
+        <v>576</v>
       </c>
       <c r="N121" t="s" s="2">
-        <v>572</v>
+        <v>564</v>
       </c>
       <c r="O121" s="2"/>
       <c r="P121" t="s" s="2">
@@ -17589,7 +17534,7 @@
         <v>81</v>
       </c>
       <c r="S121" t="s" s="2">
-        <v>585</v>
+        <v>577</v>
       </c>
       <c r="T121" t="s" s="2">
         <v>81</v>
@@ -17628,7 +17573,7 @@
         <v>81</v>
       </c>
       <c r="AF121" t="s" s="2">
-        <v>569</v>
+        <v>561</v>
       </c>
       <c r="AG121" t="s" s="2">
         <v>79</v>
@@ -17643,30 +17588,30 @@
         <v>102</v>
       </c>
       <c r="AK121" t="s" s="2">
-        <v>575</v>
+        <v>567</v>
       </c>
       <c r="AL121" t="s" s="2">
-        <v>576</v>
+        <v>568</v>
       </c>
       <c r="AM121" t="s" s="2">
-        <v>577</v>
+        <v>569</v>
       </c>
       <c r="AN121" t="s" s="2">
-        <v>578</v>
+        <v>570</v>
       </c>
       <c r="AO121" t="s" s="2">
-        <v>579</v>
+        <v>571</v>
       </c>
     </row>
     <row r="122" hidden="true">
       <c r="A122" t="s" s="2">
-        <v>586</v>
+        <v>578</v>
       </c>
       <c r="B122" t="s" s="2">
-        <v>569</v>
+        <v>561</v>
       </c>
       <c r="C122" t="s" s="2">
-        <v>587</v>
+        <v>579</v>
       </c>
       <c r="D122" t="s" s="2">
         <v>81</v>
@@ -17688,16 +17633,16 @@
         <v>81</v>
       </c>
       <c r="K122" t="s" s="2">
-        <v>588</v>
+        <v>580</v>
       </c>
       <c r="L122" t="s" s="2">
-        <v>583</v>
+        <v>575</v>
       </c>
       <c r="M122" t="s" s="2">
-        <v>584</v>
+        <v>576</v>
       </c>
       <c r="N122" t="s" s="2">
-        <v>572</v>
+        <v>564</v>
       </c>
       <c r="O122" s="2"/>
       <c r="P122" t="s" s="2">
@@ -17708,7 +17653,7 @@
         <v>81</v>
       </c>
       <c r="S122" t="s" s="2">
-        <v>589</v>
+        <v>581</v>
       </c>
       <c r="T122" t="s" s="2">
         <v>81</v>
@@ -17747,7 +17692,7 @@
         <v>81</v>
       </c>
       <c r="AF122" t="s" s="2">
-        <v>569</v>
+        <v>561</v>
       </c>
       <c r="AG122" t="s" s="2">
         <v>79</v>
@@ -17762,27 +17707,27 @@
         <v>102</v>
       </c>
       <c r="AK122" t="s" s="2">
-        <v>575</v>
+        <v>567</v>
       </c>
       <c r="AL122" t="s" s="2">
-        <v>576</v>
+        <v>568</v>
       </c>
       <c r="AM122" t="s" s="2">
-        <v>577</v>
+        <v>569</v>
       </c>
       <c r="AN122" t="s" s="2">
-        <v>578</v>
+        <v>570</v>
       </c>
       <c r="AO122" t="s" s="2">
-        <v>579</v>
+        <v>571</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="s" s="2">
-        <v>590</v>
+        <v>582</v>
       </c>
       <c r="B123" t="s" s="2">
-        <v>590</v>
+        <v>582</v>
       </c>
       <c r="C123" s="2"/>
       <c r="D123" t="s" s="2">
@@ -17808,13 +17753,13 @@
         <v>169</v>
       </c>
       <c r="L123" t="s" s="2">
-        <v>591</v>
+        <v>583</v>
       </c>
       <c r="M123" t="s" s="2">
-        <v>592</v>
+        <v>584</v>
       </c>
       <c r="N123" t="s" s="2">
-        <v>593</v>
+        <v>585</v>
       </c>
       <c r="O123" s="2"/>
       <c r="P123" t="s" s="2">
@@ -17822,7 +17767,7 @@
       </c>
       <c r="Q123" s="2"/>
       <c r="R123" t="s" s="2">
-        <v>594</v>
+        <v>586</v>
       </c>
       <c r="S123" t="s" s="2">
         <v>81</v>
@@ -17840,13 +17785,13 @@
         <v>81</v>
       </c>
       <c r="X123" t="s" s="2">
-        <v>273</v>
+        <v>270</v>
       </c>
       <c r="Y123" t="s" s="2">
-        <v>595</v>
+        <v>587</v>
       </c>
       <c r="Z123" t="s" s="2">
-        <v>596</v>
+        <v>588</v>
       </c>
       <c r="AA123" t="s" s="2">
         <v>81</v>
@@ -17864,7 +17809,7 @@
         <v>81</v>
       </c>
       <c r="AF123" t="s" s="2">
-        <v>590</v>
+        <v>582</v>
       </c>
       <c r="AG123" t="s" s="2">
         <v>90</v>
@@ -17879,16 +17824,16 @@
         <v>102</v>
       </c>
       <c r="AK123" t="s" s="2">
-        <v>597</v>
+        <v>589</v>
       </c>
       <c r="AL123" t="s" s="2">
-        <v>598</v>
+        <v>590</v>
       </c>
       <c r="AM123" t="s" s="2">
-        <v>599</v>
+        <v>591</v>
       </c>
       <c r="AN123" t="s" s="2">
-        <v>600</v>
+        <v>592</v>
       </c>
       <c r="AO123" t="s" s="2">
         <v>81</v>
@@ -17896,10 +17841,10 @@
     </row>
     <row r="124" hidden="true">
       <c r="A124" t="s" s="2">
-        <v>601</v>
+        <v>593</v>
       </c>
       <c r="B124" t="s" s="2">
-        <v>601</v>
+        <v>593</v>
       </c>
       <c r="C124" s="2"/>
       <c r="D124" t="s" s="2">
@@ -17922,16 +17867,16 @@
         <v>81</v>
       </c>
       <c r="K124" t="s" s="2">
-        <v>378</v>
+        <v>373</v>
       </c>
       <c r="L124" t="s" s="2">
-        <v>602</v>
+        <v>594</v>
       </c>
       <c r="M124" t="s" s="2">
-        <v>603</v>
+        <v>595</v>
       </c>
       <c r="N124" t="s" s="2">
-        <v>604</v>
+        <v>596</v>
       </c>
       <c r="O124" s="2"/>
       <c r="P124" t="s" s="2">
@@ -17960,10 +17905,10 @@
         <v>159</v>
       </c>
       <c r="Y124" t="s" s="2">
-        <v>605</v>
+        <v>597</v>
       </c>
       <c r="Z124" t="s" s="2">
-        <v>606</v>
+        <v>598</v>
       </c>
       <c r="AA124" t="s" s="2">
         <v>81</v>
@@ -17981,7 +17926,7 @@
         <v>81</v>
       </c>
       <c r="AF124" t="s" s="2">
-        <v>601</v>
+        <v>593</v>
       </c>
       <c r="AG124" t="s" s="2">
         <v>79</v>
@@ -17996,27 +17941,27 @@
         <v>102</v>
       </c>
       <c r="AK124" t="s" s="2">
-        <v>607</v>
+        <v>599</v>
       </c>
       <c r="AL124" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AM124" t="s" s="2">
-        <v>608</v>
+        <v>600</v>
       </c>
       <c r="AN124" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AO124" t="s" s="2">
-        <v>609</v>
+        <v>601</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="s" s="2">
-        <v>610</v>
+        <v>602</v>
       </c>
       <c r="B125" t="s" s="2">
-        <v>610</v>
+        <v>602</v>
       </c>
       <c r="C125" s="2"/>
       <c r="D125" t="s" s="2">
@@ -18042,13 +17987,13 @@
         <v>169</v>
       </c>
       <c r="L125" t="s" s="2">
-        <v>611</v>
+        <v>603</v>
       </c>
       <c r="M125" t="s" s="2">
-        <v>612</v>
+        <v>604</v>
       </c>
       <c r="N125" t="s" s="2">
-        <v>613</v>
+        <v>605</v>
       </c>
       <c r="O125" s="2"/>
       <c r="P125" t="s" s="2">
@@ -18056,7 +18001,7 @@
       </c>
       <c r="Q125" s="2"/>
       <c r="R125" t="s" s="2">
-        <v>614</v>
+        <v>606</v>
       </c>
       <c r="S125" t="s" s="2">
         <v>81</v>
@@ -18074,13 +18019,13 @@
         <v>81</v>
       </c>
       <c r="X125" t="s" s="2">
-        <v>273</v>
+        <v>270</v>
       </c>
       <c r="Y125" t="s" s="2">
-        <v>615</v>
+        <v>607</v>
       </c>
       <c r="Z125" t="s" s="2">
-        <v>616</v>
+        <v>608</v>
       </c>
       <c r="AA125" t="s" s="2">
         <v>81</v>
@@ -18098,7 +18043,7 @@
         <v>81</v>
       </c>
       <c r="AF125" t="s" s="2">
-        <v>610</v>
+        <v>602</v>
       </c>
       <c r="AG125" t="s" s="2">
         <v>90</v>
@@ -18113,16 +18058,16 @@
         <v>102</v>
       </c>
       <c r="AK125" t="s" s="2">
-        <v>617</v>
+        <v>609</v>
       </c>
       <c r="AL125" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AM125" t="s" s="2">
-        <v>618</v>
+        <v>610</v>
       </c>
       <c r="AN125" t="s" s="2">
-        <v>619</v>
+        <v>611</v>
       </c>
       <c r="AO125" t="s" s="2">
         <v>81</v>
@@ -18130,10 +18075,10 @@
     </row>
     <row r="126" hidden="true">
       <c r="A126" t="s" s="2">
-        <v>620</v>
+        <v>612</v>
       </c>
       <c r="B126" t="s" s="2">
-        <v>620</v>
+        <v>612</v>
       </c>
       <c r="C126" s="2"/>
       <c r="D126" t="s" s="2">
@@ -18156,16 +18101,16 @@
         <v>81</v>
       </c>
       <c r="K126" t="s" s="2">
-        <v>378</v>
+        <v>373</v>
       </c>
       <c r="L126" t="s" s="2">
-        <v>621</v>
+        <v>613</v>
       </c>
       <c r="M126" t="s" s="2">
-        <v>622</v>
+        <v>614</v>
       </c>
       <c r="N126" t="s" s="2">
-        <v>623</v>
+        <v>615</v>
       </c>
       <c r="O126" s="2"/>
       <c r="P126" t="s" s="2">
@@ -18194,10 +18139,10 @@
         <v>159</v>
       </c>
       <c r="Y126" t="s" s="2">
-        <v>624</v>
+        <v>616</v>
       </c>
       <c r="Z126" t="s" s="2">
-        <v>625</v>
+        <v>617</v>
       </c>
       <c r="AA126" t="s" s="2">
         <v>81</v>
@@ -18215,7 +18160,7 @@
         <v>81</v>
       </c>
       <c r="AF126" t="s" s="2">
-        <v>620</v>
+        <v>612</v>
       </c>
       <c r="AG126" t="s" s="2">
         <v>79</v>
@@ -18233,24 +18178,24 @@
         <v>81</v>
       </c>
       <c r="AL126" t="s" s="2">
-        <v>626</v>
+        <v>618</v>
       </c>
       <c r="AM126" t="s" s="2">
-        <v>627</v>
+        <v>619</v>
       </c>
       <c r="AN126" t="s" s="2">
-        <v>619</v>
+        <v>611</v>
       </c>
       <c r="AO126" t="s" s="2">
-        <v>609</v>
+        <v>601</v>
       </c>
     </row>
     <row r="127" hidden="true">
       <c r="A127" t="s" s="2">
-        <v>628</v>
+        <v>620</v>
       </c>
       <c r="B127" t="s" s="2">
-        <v>628</v>
+        <v>620</v>
       </c>
       <c r="C127" s="2"/>
       <c r="D127" t="s" s="2">
@@ -18276,10 +18221,10 @@
         <v>169</v>
       </c>
       <c r="L127" t="s" s="2">
-        <v>629</v>
+        <v>621</v>
       </c>
       <c r="M127" t="s" s="2">
-        <v>630</v>
+        <v>622</v>
       </c>
       <c r="N127" s="2"/>
       <c r="O127" s="2"/>
@@ -18306,13 +18251,13 @@
         <v>81</v>
       </c>
       <c r="X127" t="s" s="2">
-        <v>273</v>
+        <v>270</v>
       </c>
       <c r="Y127" t="s" s="2">
-        <v>631</v>
+        <v>623</v>
       </c>
       <c r="Z127" t="s" s="2">
-        <v>632</v>
+        <v>624</v>
       </c>
       <c r="AA127" t="s" s="2">
         <v>81</v>
@@ -18330,7 +18275,7 @@
         <v>81</v>
       </c>
       <c r="AF127" t="s" s="2">
-        <v>628</v>
+        <v>620</v>
       </c>
       <c r="AG127" t="s" s="2">
         <v>79</v>
@@ -18345,16 +18290,16 @@
         <v>102</v>
       </c>
       <c r="AK127" t="s" s="2">
-        <v>633</v>
+        <v>625</v>
       </c>
       <c r="AL127" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AM127" t="s" s="2">
-        <v>634</v>
+        <v>626</v>
       </c>
       <c r="AN127" t="s" s="2">
-        <v>635</v>
+        <v>627</v>
       </c>
       <c r="AO127" t="s" s="2">
         <v>81</v>
@@ -18362,10 +18307,10 @@
     </row>
     <row r="128" hidden="true">
       <c r="A128" t="s" s="2">
-        <v>636</v>
+        <v>628</v>
       </c>
       <c r="B128" t="s" s="2">
-        <v>636</v>
+        <v>628</v>
       </c>
       <c r="C128" s="2"/>
       <c r="D128" t="s" s="2">
@@ -18391,13 +18336,13 @@
         <v>226</v>
       </c>
       <c r="L128" t="s" s="2">
-        <v>637</v>
+        <v>629</v>
       </c>
       <c r="M128" t="s" s="2">
-        <v>638</v>
+        <v>630</v>
       </c>
       <c r="N128" t="s" s="2">
-        <v>639</v>
+        <v>631</v>
       </c>
       <c r="O128" s="2"/>
       <c r="P128" t="s" s="2">
@@ -18447,7 +18392,7 @@
         <v>81</v>
       </c>
       <c r="AF128" t="s" s="2">
-        <v>636</v>
+        <v>628</v>
       </c>
       <c r="AG128" t="s" s="2">
         <v>79</v>
@@ -18468,7 +18413,7 @@
         <v>81</v>
       </c>
       <c r="AM128" t="s" s="2">
-        <v>640</v>
+        <v>632</v>
       </c>
       <c r="AN128" t="s" s="2">
         <v>81</v>
@@ -18479,10 +18424,10 @@
     </row>
     <row r="129" hidden="true">
       <c r="A129" t="s" s="2">
-        <v>641</v>
+        <v>633</v>
       </c>
       <c r="B129" t="s" s="2">
-        <v>641</v>
+        <v>633</v>
       </c>
       <c r="C129" s="2"/>
       <c r="D129" t="s" s="2">
@@ -18505,13 +18450,13 @@
         <v>91</v>
       </c>
       <c r="K129" t="s" s="2">
-        <v>642</v>
+        <v>634</v>
       </c>
       <c r="L129" t="s" s="2">
-        <v>643</v>
+        <v>635</v>
       </c>
       <c r="M129" t="s" s="2">
-        <v>644</v>
+        <v>636</v>
       </c>
       <c r="N129" s="2"/>
       <c r="O129" s="2"/>
@@ -18562,7 +18507,7 @@
         <v>81</v>
       </c>
       <c r="AF129" t="s" s="2">
-        <v>641</v>
+        <v>633</v>
       </c>
       <c r="AG129" t="s" s="2">
         <v>79</v>
@@ -18583,7 +18528,7 @@
         <v>81</v>
       </c>
       <c r="AM129" t="s" s="2">
-        <v>645</v>
+        <v>637</v>
       </c>
       <c r="AN129" t="s" s="2">
         <v>81</v>
@@ -18594,10 +18539,10 @@
     </row>
     <row r="130">
       <c r="A130" t="s" s="2">
-        <v>646</v>
+        <v>638</v>
       </c>
       <c r="B130" t="s" s="2">
-        <v>646</v>
+        <v>638</v>
       </c>
       <c r="C130" s="2"/>
       <c r="D130" t="s" s="2">
@@ -18620,16 +18565,16 @@
         <v>91</v>
       </c>
       <c r="K130" t="s" s="2">
-        <v>647</v>
+        <v>639</v>
       </c>
       <c r="L130" t="s" s="2">
-        <v>648</v>
+        <v>640</v>
       </c>
       <c r="M130" t="s" s="2">
-        <v>649</v>
+        <v>641</v>
       </c>
       <c r="N130" t="s" s="2">
-        <v>650</v>
+        <v>642</v>
       </c>
       <c r="O130" s="2"/>
       <c r="P130" t="s" s="2">
@@ -18679,7 +18624,7 @@
         <v>81</v>
       </c>
       <c r="AF130" t="s" s="2">
-        <v>646</v>
+        <v>638</v>
       </c>
       <c r="AG130" t="s" s="2">
         <v>90</v>
@@ -18694,27 +18639,27 @@
         <v>102</v>
       </c>
       <c r="AK130" t="s" s="2">
-        <v>651</v>
+        <v>643</v>
       </c>
       <c r="AL130" t="s" s="2">
-        <v>652</v>
+        <v>644</v>
       </c>
       <c r="AM130" t="s" s="2">
-        <v>653</v>
+        <v>645</v>
       </c>
       <c r="AN130" t="s" s="2">
-        <v>654</v>
+        <v>646</v>
       </c>
       <c r="AO130" t="s" s="2">
-        <v>655</v>
+        <v>647</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="s" s="2">
-        <v>656</v>
+        <v>648</v>
       </c>
       <c r="B131" t="s" s="2">
-        <v>656</v>
+        <v>648</v>
       </c>
       <c r="C131" s="2"/>
       <c r="D131" t="s" s="2">
@@ -18737,16 +18682,16 @@
         <v>91</v>
       </c>
       <c r="K131" t="s" s="2">
-        <v>657</v>
+        <v>649</v>
       </c>
       <c r="L131" t="s" s="2">
-        <v>658</v>
+        <v>650</v>
       </c>
       <c r="M131" t="s" s="2">
-        <v>659</v>
+        <v>651</v>
       </c>
       <c r="N131" t="s" s="2">
-        <v>660</v>
+        <v>652</v>
       </c>
       <c r="O131" s="2"/>
       <c r="P131" t="s" s="2">
@@ -18796,7 +18741,7 @@
         <v>81</v>
       </c>
       <c r="AF131" t="s" s="2">
-        <v>656</v>
+        <v>648</v>
       </c>
       <c r="AG131" t="s" s="2">
         <v>90</v>
@@ -18808,30 +18753,30 @@
         <v>152</v>
       </c>
       <c r="AJ131" t="s" s="2">
-        <v>423</v>
+        <v>653</v>
       </c>
       <c r="AK131" t="s" s="2">
-        <v>661</v>
+        <v>654</v>
       </c>
       <c r="AL131" t="s" s="2">
-        <v>662</v>
+        <v>655</v>
       </c>
       <c r="AM131" t="s" s="2">
-        <v>663</v>
+        <v>656</v>
       </c>
       <c r="AN131" t="s" s="2">
-        <v>664</v>
+        <v>657</v>
       </c>
       <c r="AO131" t="s" s="2">
-        <v>665</v>
+        <v>658</v>
       </c>
     </row>
     <row r="132" hidden="true">
       <c r="A132" t="s" s="2">
-        <v>666</v>
+        <v>659</v>
       </c>
       <c r="B132" t="s" s="2">
-        <v>666</v>
+        <v>659</v>
       </c>
       <c r="C132" s="2"/>
       <c r="D132" t="s" s="2">
@@ -18943,10 +18888,10 @@
     </row>
     <row r="133" hidden="true">
       <c r="A133" t="s" s="2">
-        <v>667</v>
+        <v>660</v>
       </c>
       <c r="B133" t="s" s="2">
-        <v>667</v>
+        <v>660</v>
       </c>
       <c r="C133" s="2"/>
       <c r="D133" t="s" s="2">
@@ -19060,10 +19005,10 @@
     </row>
     <row r="134" hidden="true">
       <c r="A134" t="s" s="2">
-        <v>668</v>
+        <v>661</v>
       </c>
       <c r="B134" t="s" s="2">
-        <v>668</v>
+        <v>661</v>
       </c>
       <c r="C134" s="2"/>
       <c r="D134" t="s" s="2">
@@ -19089,13 +19034,13 @@
         <v>104</v>
       </c>
       <c r="L134" t="s" s="2">
-        <v>669</v>
+        <v>662</v>
       </c>
       <c r="M134" t="s" s="2">
-        <v>670</v>
+        <v>663</v>
       </c>
       <c r="N134" t="s" s="2">
-        <v>671</v>
+        <v>664</v>
       </c>
       <c r="O134" s="2"/>
       <c r="P134" t="s" s="2">
@@ -19145,7 +19090,7 @@
         <v>81</v>
       </c>
       <c r="AF134" t="s" s="2">
-        <v>672</v>
+        <v>665</v>
       </c>
       <c r="AG134" t="s" s="2">
         <v>79</v>
@@ -19154,7 +19099,7 @@
         <v>90</v>
       </c>
       <c r="AI134" t="s" s="2">
-        <v>673</v>
+        <v>666</v>
       </c>
       <c r="AJ134" t="s" s="2">
         <v>102</v>
@@ -19177,10 +19122,10 @@
     </row>
     <row r="135" hidden="true">
       <c r="A135" t="s" s="2">
-        <v>674</v>
+        <v>667</v>
       </c>
       <c r="B135" t="s" s="2">
-        <v>674</v>
+        <v>667</v>
       </c>
       <c r="C135" s="2"/>
       <c r="D135" t="s" s="2">
@@ -19206,13 +19151,13 @@
         <v>132</v>
       </c>
       <c r="L135" t="s" s="2">
-        <v>675</v>
+        <v>668</v>
       </c>
       <c r="M135" t="s" s="2">
-        <v>676</v>
+        <v>669</v>
       </c>
       <c r="N135" t="s" s="2">
-        <v>677</v>
+        <v>670</v>
       </c>
       <c r="O135" s="2"/>
       <c r="P135" t="s" s="2">
@@ -19241,10 +19186,10 @@
         <v>148</v>
       </c>
       <c r="Y135" t="s" s="2">
-        <v>678</v>
+        <v>671</v>
       </c>
       <c r="Z135" t="s" s="2">
-        <v>679</v>
+        <v>672</v>
       </c>
       <c r="AA135" t="s" s="2">
         <v>81</v>
@@ -19262,7 +19207,7 @@
         <v>81</v>
       </c>
       <c r="AF135" t="s" s="2">
-        <v>680</v>
+        <v>673</v>
       </c>
       <c r="AG135" t="s" s="2">
         <v>79</v>
@@ -19294,10 +19239,10 @@
     </row>
     <row r="136">
       <c r="A136" t="s" s="2">
-        <v>681</v>
+        <v>674</v>
       </c>
       <c r="B136" t="s" s="2">
-        <v>681</v>
+        <v>674</v>
       </c>
       <c r="C136" s="2"/>
       <c r="D136" t="s" s="2">
@@ -19320,16 +19265,16 @@
         <v>91</v>
       </c>
       <c r="K136" t="s" s="2">
-        <v>682</v>
+        <v>675</v>
       </c>
       <c r="L136" t="s" s="2">
-        <v>583</v>
+        <v>575</v>
       </c>
       <c r="M136" t="s" s="2">
-        <v>584</v>
+        <v>576</v>
       </c>
       <c r="N136" t="s" s="2">
-        <v>683</v>
+        <v>676</v>
       </c>
       <c r="O136" s="2"/>
       <c r="P136" t="s" s="2">
@@ -19379,7 +19324,7 @@
         <v>81</v>
       </c>
       <c r="AF136" t="s" s="2">
-        <v>684</v>
+        <v>677</v>
       </c>
       <c r="AG136" t="s" s="2">
         <v>79</v>
@@ -19400,21 +19345,21 @@
         <v>81</v>
       </c>
       <c r="AM136" t="s" s="2">
-        <v>685</v>
+        <v>678</v>
       </c>
       <c r="AN136" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AO136" t="s" s="2">
-        <v>686</v>
+        <v>679</v>
       </c>
     </row>
     <row r="137" hidden="true">
       <c r="A137" t="s" s="2">
-        <v>687</v>
+        <v>680</v>
       </c>
       <c r="B137" t="s" s="2">
-        <v>687</v>
+        <v>680</v>
       </c>
       <c r="C137" s="2"/>
       <c r="D137" t="s" s="2">
@@ -19440,13 +19385,13 @@
         <v>104</v>
       </c>
       <c r="L137" t="s" s="2">
-        <v>688</v>
+        <v>681</v>
       </c>
       <c r="M137" t="s" s="2">
-        <v>689</v>
+        <v>682</v>
       </c>
       <c r="N137" t="s" s="2">
-        <v>690</v>
+        <v>683</v>
       </c>
       <c r="O137" s="2"/>
       <c r="P137" t="s" s="2">
@@ -19496,7 +19441,7 @@
         <v>81</v>
       </c>
       <c r="AF137" t="s" s="2">
-        <v>691</v>
+        <v>684</v>
       </c>
       <c r="AG137" t="s" s="2">
         <v>79</v>
@@ -19528,10 +19473,10 @@
     </row>
     <row r="138" hidden="true">
       <c r="A138" t="s" s="2">
-        <v>692</v>
+        <v>685</v>
       </c>
       <c r="B138" t="s" s="2">
-        <v>692</v>
+        <v>685</v>
       </c>
       <c r="C138" s="2"/>
       <c r="D138" t="s" s="2">
@@ -19554,16 +19499,16 @@
         <v>81</v>
       </c>
       <c r="K138" t="s" s="2">
-        <v>693</v>
+        <v>686</v>
       </c>
       <c r="L138" t="s" s="2">
-        <v>694</v>
+        <v>687</v>
       </c>
       <c r="M138" t="s" s="2">
-        <v>695</v>
+        <v>688</v>
       </c>
       <c r="N138" t="s" s="2">
-        <v>696</v>
+        <v>689</v>
       </c>
       <c r="O138" s="2"/>
       <c r="P138" t="s" s="2">
@@ -19613,7 +19558,7 @@
         <v>81</v>
       </c>
       <c r="AF138" t="s" s="2">
-        <v>692</v>
+        <v>685</v>
       </c>
       <c r="AG138" t="s" s="2">
         <v>79</v>
@@ -19625,30 +19570,30 @@
         <v>152</v>
       </c>
       <c r="AJ138" t="s" s="2">
-        <v>423</v>
+        <v>653</v>
       </c>
       <c r="AK138" t="s" s="2">
-        <v>697</v>
+        <v>690</v>
       </c>
       <c r="AL138" t="s" s="2">
-        <v>598</v>
+        <v>590</v>
       </c>
       <c r="AM138" t="s" s="2">
-        <v>698</v>
+        <v>691</v>
       </c>
       <c r="AN138" t="s" s="2">
-        <v>699</v>
+        <v>692</v>
       </c>
       <c r="AO138" t="s" s="2">
-        <v>700</v>
+        <v>693</v>
       </c>
     </row>
     <row r="139" hidden="true">
       <c r="A139" t="s" s="2">
-        <v>701</v>
+        <v>694</v>
       </c>
       <c r="B139" t="s" s="2">
-        <v>701</v>
+        <v>694</v>
       </c>
       <c r="C139" s="2"/>
       <c r="D139" t="s" s="2">
@@ -19671,16 +19616,16 @@
         <v>81</v>
       </c>
       <c r="K139" t="s" s="2">
-        <v>702</v>
+        <v>695</v>
       </c>
       <c r="L139" t="s" s="2">
-        <v>703</v>
+        <v>696</v>
       </c>
       <c r="M139" t="s" s="2">
-        <v>704</v>
+        <v>697</v>
       </c>
       <c r="N139" t="s" s="2">
-        <v>705</v>
+        <v>698</v>
       </c>
       <c r="O139" s="2"/>
       <c r="P139" t="s" s="2">
@@ -19730,7 +19675,7 @@
         <v>81</v>
       </c>
       <c r="AF139" t="s" s="2">
-        <v>701</v>
+        <v>694</v>
       </c>
       <c r="AG139" t="s" s="2">
         <v>79</v>
@@ -19742,19 +19687,19 @@
         <v>152</v>
       </c>
       <c r="AJ139" t="s" s="2">
-        <v>423</v>
+        <v>653</v>
       </c>
       <c r="AK139" t="s" s="2">
-        <v>706</v>
+        <v>699</v>
       </c>
       <c r="AL139" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AM139" t="s" s="2">
-        <v>707</v>
+        <v>700</v>
       </c>
       <c r="AN139" t="s" s="2">
-        <v>699</v>
+        <v>692</v>
       </c>
       <c r="AO139" t="s" s="2">
         <v>81</v>
@@ -19762,10 +19707,10 @@
     </row>
     <row r="140">
       <c r="A140" t="s" s="2">
-        <v>708</v>
+        <v>701</v>
       </c>
       <c r="B140" t="s" s="2">
-        <v>708</v>
+        <v>701</v>
       </c>
       <c r="C140" s="2"/>
       <c r="D140" t="s" s="2">
@@ -19788,13 +19733,13 @@
         <v>91</v>
       </c>
       <c r="K140" t="s" s="2">
-        <v>340</v>
+        <v>335</v>
       </c>
       <c r="L140" t="s" s="2">
-        <v>709</v>
+        <v>702</v>
       </c>
       <c r="M140" t="s" s="2">
-        <v>710</v>
+        <v>703</v>
       </c>
       <c r="N140" s="2"/>
       <c r="O140" s="2"/>
@@ -19845,7 +19790,7 @@
         <v>81</v>
       </c>
       <c r="AF140" t="s" s="2">
-        <v>708</v>
+        <v>701</v>
       </c>
       <c r="AG140" t="s" s="2">
         <v>79</v>
@@ -19860,27 +19805,27 @@
         <v>102</v>
       </c>
       <c r="AK140" t="s" s="2">
-        <v>711</v>
+        <v>704</v>
       </c>
       <c r="AL140" t="s" s="2">
-        <v>712</v>
+        <v>705</v>
       </c>
       <c r="AM140" t="s" s="2">
-        <v>713</v>
+        <v>706</v>
       </c>
       <c r="AN140" t="s" s="2">
-        <v>714</v>
+        <v>707</v>
       </c>
       <c r="AO140" t="s" s="2">
-        <v>715</v>
+        <v>708</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="s" s="2">
-        <v>716</v>
+        <v>709</v>
       </c>
       <c r="B141" t="s" s="2">
-        <v>716</v>
+        <v>709</v>
       </c>
       <c r="C141" s="2"/>
       <c r="D141" t="s" s="2">
@@ -19903,16 +19848,16 @@
         <v>91</v>
       </c>
       <c r="K141" t="s" s="2">
-        <v>717</v>
+        <v>710</v>
       </c>
       <c r="L141" t="s" s="2">
-        <v>718</v>
+        <v>711</v>
       </c>
       <c r="M141" t="s" s="2">
-        <v>719</v>
+        <v>712</v>
       </c>
       <c r="N141" t="s" s="2">
-        <v>705</v>
+        <v>698</v>
       </c>
       <c r="O141" s="2"/>
       <c r="P141" t="s" s="2">
@@ -19962,7 +19907,7 @@
         <v>81</v>
       </c>
       <c r="AF141" t="s" s="2">
-        <v>716</v>
+        <v>709</v>
       </c>
       <c r="AG141" t="s" s="2">
         <v>79</v>
@@ -19974,19 +19919,19 @@
         <v>152</v>
       </c>
       <c r="AJ141" t="s" s="2">
-        <v>423</v>
+        <v>653</v>
       </c>
       <c r="AK141" t="s" s="2">
-        <v>720</v>
+        <v>713</v>
       </c>
       <c r="AL141" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AM141" t="s" s="2">
-        <v>663</v>
+        <v>656</v>
       </c>
       <c r="AN141" t="s" s="2">
-        <v>721</v>
+        <v>714</v>
       </c>
       <c r="AO141" t="s" s="2">
         <v>81</v>
@@ -19994,10 +19939,10 @@
     </row>
     <row r="142" hidden="true">
       <c r="A142" t="s" s="2">
-        <v>722</v>
+        <v>715</v>
       </c>
       <c r="B142" t="s" s="2">
-        <v>722</v>
+        <v>715</v>
       </c>
       <c r="C142" s="2"/>
       <c r="D142" t="s" s="2">
@@ -20020,16 +19965,16 @@
         <v>81</v>
       </c>
       <c r="K142" t="s" s="2">
-        <v>723</v>
+        <v>716</v>
       </c>
       <c r="L142" t="s" s="2">
-        <v>724</v>
+        <v>717</v>
       </c>
       <c r="M142" t="s" s="2">
-        <v>725</v>
+        <v>718</v>
       </c>
       <c r="N142" t="s" s="2">
-        <v>705</v>
+        <v>698</v>
       </c>
       <c r="O142" s="2"/>
       <c r="P142" t="s" s="2">
@@ -20079,7 +20024,7 @@
         <v>81</v>
       </c>
       <c r="AF142" t="s" s="2">
-        <v>722</v>
+        <v>715</v>
       </c>
       <c r="AG142" t="s" s="2">
         <v>79</v>
@@ -20091,19 +20036,19 @@
         <v>152</v>
       </c>
       <c r="AJ142" t="s" s="2">
-        <v>423</v>
+        <v>653</v>
       </c>
       <c r="AK142" t="s" s="2">
-        <v>726</v>
+        <v>719</v>
       </c>
       <c r="AL142" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AM142" t="s" s="2">
-        <v>727</v>
+        <v>720</v>
       </c>
       <c r="AN142" t="s" s="2">
-        <v>728</v>
+        <v>721</v>
       </c>
       <c r="AO142" t="s" s="2">
         <v>81</v>
@@ -20111,10 +20056,10 @@
     </row>
     <row r="143" hidden="true">
       <c r="A143" t="s" s="2">
-        <v>729</v>
+        <v>722</v>
       </c>
       <c r="B143" t="s" s="2">
-        <v>729</v>
+        <v>722</v>
       </c>
       <c r="C143" s="2"/>
       <c r="D143" t="s" s="2">
@@ -20137,16 +20082,16 @@
         <v>91</v>
       </c>
       <c r="K143" t="s" s="2">
-        <v>378</v>
+        <v>373</v>
       </c>
       <c r="L143" t="s" s="2">
-        <v>730</v>
+        <v>723</v>
       </c>
       <c r="M143" t="s" s="2">
-        <v>731</v>
+        <v>724</v>
       </c>
       <c r="N143" t="s" s="2">
-        <v>732</v>
+        <v>725</v>
       </c>
       <c r="O143" s="2"/>
       <c r="P143" t="s" s="2">
@@ -20175,10 +20120,10 @@
         <v>159</v>
       </c>
       <c r="Y143" t="s" s="2">
-        <v>733</v>
+        <v>726</v>
       </c>
       <c r="Z143" t="s" s="2">
-        <v>734</v>
+        <v>727</v>
       </c>
       <c r="AA143" t="s" s="2">
         <v>81</v>
@@ -20196,7 +20141,7 @@
         <v>81</v>
       </c>
       <c r="AF143" t="s" s="2">
-        <v>729</v>
+        <v>722</v>
       </c>
       <c r="AG143" t="s" s="2">
         <v>79</v>
@@ -20211,27 +20156,27 @@
         <v>102</v>
       </c>
       <c r="AK143" t="s" s="2">
-        <v>735</v>
+        <v>728</v>
       </c>
       <c r="AL143" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AM143" t="s" s="2">
-        <v>736</v>
+        <v>729</v>
       </c>
       <c r="AN143" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AO143" t="s" s="2">
-        <v>609</v>
+        <v>601</v>
       </c>
     </row>
     <row r="144" hidden="true">
       <c r="A144" t="s" s="2">
-        <v>737</v>
+        <v>730</v>
       </c>
       <c r="B144" t="s" s="2">
-        <v>737</v>
+        <v>730</v>
       </c>
       <c r="C144" s="2"/>
       <c r="D144" t="s" s="2">
@@ -20254,16 +20199,16 @@
         <v>81</v>
       </c>
       <c r="K144" t="s" s="2">
-        <v>738</v>
+        <v>731</v>
       </c>
       <c r="L144" t="s" s="2">
-        <v>739</v>
+        <v>732</v>
       </c>
       <c r="M144" t="s" s="2">
-        <v>740</v>
+        <v>733</v>
       </c>
       <c r="N144" t="s" s="2">
-        <v>705</v>
+        <v>698</v>
       </c>
       <c r="O144" s="2"/>
       <c r="P144" t="s" s="2">
@@ -20313,7 +20258,7 @@
         <v>81</v>
       </c>
       <c r="AF144" t="s" s="2">
-        <v>737</v>
+        <v>730</v>
       </c>
       <c r="AG144" t="s" s="2">
         <v>79</v>
@@ -20325,7 +20270,7 @@
         <v>152</v>
       </c>
       <c r="AJ144" t="s" s="2">
-        <v>423</v>
+        <v>653</v>
       </c>
       <c r="AK144" t="s" s="2">
         <v>81</v>
@@ -20334,10 +20279,10 @@
         <v>81</v>
       </c>
       <c r="AM144" t="s" s="2">
-        <v>741</v>
+        <v>734</v>
       </c>
       <c r="AN144" t="s" s="2">
-        <v>742</v>
+        <v>735</v>
       </c>
       <c r="AO144" t="s" s="2">
         <v>81</v>
@@ -20345,10 +20290,10 @@
     </row>
     <row r="145" hidden="true">
       <c r="A145" t="s" s="2">
-        <v>743</v>
+        <v>736</v>
       </c>
       <c r="B145" t="s" s="2">
-        <v>743</v>
+        <v>736</v>
       </c>
       <c r="C145" s="2"/>
       <c r="D145" t="s" s="2">
@@ -20371,16 +20316,16 @@
         <v>81</v>
       </c>
       <c r="K145" t="s" s="2">
-        <v>378</v>
+        <v>373</v>
       </c>
       <c r="L145" t="s" s="2">
-        <v>744</v>
+        <v>737</v>
       </c>
       <c r="M145" t="s" s="2">
-        <v>745</v>
+        <v>738</v>
       </c>
       <c r="N145" t="s" s="2">
-        <v>746</v>
+        <v>739</v>
       </c>
       <c r="O145" s="2"/>
       <c r="P145" t="s" s="2">
@@ -20409,10 +20354,10 @@
         <v>159</v>
       </c>
       <c r="Y145" t="s" s="2">
-        <v>747</v>
+        <v>740</v>
       </c>
       <c r="Z145" t="s" s="2">
-        <v>748</v>
+        <v>741</v>
       </c>
       <c r="AA145" t="s" s="2">
         <v>81</v>
@@ -20430,7 +20375,7 @@
         <v>81</v>
       </c>
       <c r="AF145" t="s" s="2">
-        <v>743</v>
+        <v>736</v>
       </c>
       <c r="AG145" t="s" s="2">
         <v>79</v>
@@ -20445,27 +20390,27 @@
         <v>102</v>
       </c>
       <c r="AK145" t="s" s="2">
-        <v>749</v>
+        <v>742</v>
       </c>
       <c r="AL145" t="s" s="2">
-        <v>750</v>
+        <v>743</v>
       </c>
       <c r="AM145" t="s" s="2">
-        <v>751</v>
+        <v>744</v>
       </c>
       <c r="AN145" t="s" s="2">
-        <v>752</v>
+        <v>745</v>
       </c>
       <c r="AO145" t="s" s="2">
-        <v>753</v>
+        <v>746</v>
       </c>
     </row>
     <row r="146" hidden="true">
       <c r="A146" t="s" s="2">
-        <v>754</v>
+        <v>747</v>
       </c>
       <c r="B146" t="s" s="2">
-        <v>754</v>
+        <v>747</v>
       </c>
       <c r="C146" s="2"/>
       <c r="D146" t="s" s="2">
@@ -20488,16 +20433,16 @@
         <v>81</v>
       </c>
       <c r="K146" t="s" s="2">
-        <v>755</v>
+        <v>748</v>
       </c>
       <c r="L146" t="s" s="2">
-        <v>756</v>
+        <v>749</v>
       </c>
       <c r="M146" t="s" s="2">
-        <v>757</v>
+        <v>750</v>
       </c>
       <c r="N146" t="s" s="2">
-        <v>758</v>
+        <v>751</v>
       </c>
       <c r="O146" s="2"/>
       <c r="P146" t="s" s="2">
@@ -20547,7 +20492,7 @@
         <v>81</v>
       </c>
       <c r="AF146" t="s" s="2">
-        <v>754</v>
+        <v>747</v>
       </c>
       <c r="AG146" t="s" s="2">
         <v>79</v>
@@ -20559,19 +20504,19 @@
         <v>152</v>
       </c>
       <c r="AJ146" t="s" s="2">
-        <v>423</v>
+        <v>653</v>
       </c>
       <c r="AK146" t="s" s="2">
-        <v>759</v>
+        <v>752</v>
       </c>
       <c r="AL146" t="s" s="2">
-        <v>598</v>
+        <v>590</v>
       </c>
       <c r="AM146" t="s" s="2">
-        <v>760</v>
+        <v>753</v>
       </c>
       <c r="AN146" t="s" s="2">
-        <v>752</v>
+        <v>745</v>
       </c>
       <c r="AO146" t="s" s="2">
         <v>81</v>
@@ -20579,10 +20524,10 @@
     </row>
     <row r="147" hidden="true">
       <c r="A147" t="s" s="2">
-        <v>761</v>
+        <v>754</v>
       </c>
       <c r="B147" t="s" s="2">
-        <v>761</v>
+        <v>754</v>
       </c>
       <c r="C147" s="2"/>
       <c r="D147" t="s" s="2">
@@ -20605,16 +20550,16 @@
         <v>91</v>
       </c>
       <c r="K147" t="s" s="2">
-        <v>762</v>
+        <v>755</v>
       </c>
       <c r="L147" t="s" s="2">
-        <v>763</v>
+        <v>756</v>
       </c>
       <c r="M147" t="s" s="2">
-        <v>764</v>
+        <v>757</v>
       </c>
       <c r="N147" t="s" s="2">
-        <v>765</v>
+        <v>758</v>
       </c>
       <c r="O147" s="2"/>
       <c r="P147" t="s" s="2">
@@ -20664,7 +20609,7 @@
         <v>81</v>
       </c>
       <c r="AF147" t="s" s="2">
-        <v>761</v>
+        <v>754</v>
       </c>
       <c r="AG147" t="s" s="2">
         <v>79</v>
@@ -20679,13 +20624,13 @@
         <v>102</v>
       </c>
       <c r="AK147" t="s" s="2">
-        <v>766</v>
+        <v>759</v>
       </c>
       <c r="AL147" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AM147" t="s" s="2">
-        <v>767</v>
+        <v>760</v>
       </c>
       <c r="AN147" t="s" s="2">
         <v>81</v>
@@ -20696,10 +20641,10 @@
     </row>
     <row r="148" hidden="true">
       <c r="A148" t="s" s="2">
-        <v>768</v>
+        <v>761</v>
       </c>
       <c r="B148" t="s" s="2">
-        <v>768</v>
+        <v>761</v>
       </c>
       <c r="C148" s="2"/>
       <c r="D148" t="s" s="2">
@@ -20725,13 +20670,13 @@
         <v>132</v>
       </c>
       <c r="L148" t="s" s="2">
-        <v>769</v>
+        <v>762</v>
       </c>
       <c r="M148" t="s" s="2">
-        <v>770</v>
+        <v>763</v>
       </c>
       <c r="N148" t="s" s="2">
-        <v>292</v>
+        <v>764</v>
       </c>
       <c r="O148" s="2"/>
       <c r="P148" t="s" s="2">
@@ -20781,7 +20726,7 @@
         <v>81</v>
       </c>
       <c r="AF148" t="s" s="2">
-        <v>768</v>
+        <v>761</v>
       </c>
       <c r="AG148" t="s" s="2">
         <v>79</v>
@@ -20802,7 +20747,7 @@
         <v>81</v>
       </c>
       <c r="AM148" t="s" s="2">
-        <v>767</v>
+        <v>760</v>
       </c>
       <c r="AN148" t="s" s="2">
         <v>81</v>
@@ -20813,10 +20758,10 @@
     </row>
     <row r="149">
       <c r="A149" t="s" s="2">
-        <v>771</v>
+        <v>765</v>
       </c>
       <c r="B149" t="s" s="2">
-        <v>771</v>
+        <v>765</v>
       </c>
       <c r="C149" s="2"/>
       <c r="D149" t="s" s="2">
@@ -20839,16 +20784,16 @@
         <v>91</v>
       </c>
       <c r="K149" t="s" s="2">
-        <v>772</v>
+        <v>766</v>
       </c>
       <c r="L149" t="s" s="2">
-        <v>773</v>
+        <v>767</v>
       </c>
       <c r="M149" t="s" s="2">
-        <v>774</v>
+        <v>768</v>
       </c>
       <c r="N149" t="s" s="2">
-        <v>705</v>
+        <v>698</v>
       </c>
       <c r="O149" s="2"/>
       <c r="P149" t="s" s="2">
@@ -20898,7 +20843,7 @@
         <v>81</v>
       </c>
       <c r="AF149" t="s" s="2">
-        <v>771</v>
+        <v>765</v>
       </c>
       <c r="AG149" t="s" s="2">
         <v>79</v>
@@ -20910,16 +20855,16 @@
         <v>152</v>
       </c>
       <c r="AJ149" t="s" s="2">
-        <v>423</v>
+        <v>653</v>
       </c>
       <c r="AK149" t="s" s="2">
-        <v>775</v>
+        <v>769</v>
       </c>
       <c r="AL149" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AM149" t="s" s="2">
-        <v>776</v>
+        <v>770</v>
       </c>
       <c r="AN149" t="s" s="2">
         <v>81</v>
@@ -20930,10 +20875,10 @@
     </row>
     <row r="150" hidden="true">
       <c r="A150" t="s" s="2">
-        <v>777</v>
+        <v>771</v>
       </c>
       <c r="B150" t="s" s="2">
-        <v>777</v>
+        <v>771</v>
       </c>
       <c r="C150" s="2"/>
       <c r="D150" t="s" s="2">
@@ -21045,10 +20990,10 @@
     </row>
     <row r="151" hidden="true">
       <c r="A151" t="s" s="2">
-        <v>778</v>
+        <v>772</v>
       </c>
       <c r="B151" t="s" s="2">
-        <v>778</v>
+        <v>772</v>
       </c>
       <c r="C151" s="2"/>
       <c r="D151" t="s" s="2">
@@ -21162,10 +21107,10 @@
     </row>
     <row r="152">
       <c r="A152" t="s" s="2">
-        <v>779</v>
+        <v>773</v>
       </c>
       <c r="B152" t="s" s="2">
-        <v>779</v>
+        <v>773</v>
       </c>
       <c r="C152" s="2"/>
       <c r="D152" t="s" s="2">
@@ -21191,13 +21136,13 @@
         <v>104</v>
       </c>
       <c r="L152" t="s" s="2">
-        <v>669</v>
+        <v>662</v>
       </c>
       <c r="M152" t="s" s="2">
-        <v>670</v>
+        <v>663</v>
       </c>
       <c r="N152" t="s" s="2">
-        <v>671</v>
+        <v>664</v>
       </c>
       <c r="O152" s="2"/>
       <c r="P152" t="s" s="2">
@@ -21247,7 +21192,7 @@
         <v>81</v>
       </c>
       <c r="AF152" t="s" s="2">
-        <v>672</v>
+        <v>665</v>
       </c>
       <c r="AG152" t="s" s="2">
         <v>79</v>
@@ -21256,7 +21201,7 @@
         <v>90</v>
       </c>
       <c r="AI152" t="s" s="2">
-        <v>673</v>
+        <v>666</v>
       </c>
       <c r="AJ152" t="s" s="2">
         <v>102</v>
@@ -21279,10 +21224,10 @@
     </row>
     <row r="153" hidden="true">
       <c r="A153" t="s" s="2">
-        <v>780</v>
+        <v>774</v>
       </c>
       <c r="B153" t="s" s="2">
-        <v>780</v>
+        <v>774</v>
       </c>
       <c r="C153" s="2"/>
       <c r="D153" t="s" s="2">
@@ -21308,13 +21253,13 @@
         <v>132</v>
       </c>
       <c r="L153" t="s" s="2">
-        <v>675</v>
+        <v>668</v>
       </c>
       <c r="M153" t="s" s="2">
-        <v>676</v>
+        <v>669</v>
       </c>
       <c r="N153" t="s" s="2">
-        <v>677</v>
+        <v>670</v>
       </c>
       <c r="O153" s="2"/>
       <c r="P153" t="s" s="2">
@@ -21343,10 +21288,10 @@
         <v>148</v>
       </c>
       <c r="Y153" t="s" s="2">
-        <v>678</v>
+        <v>671</v>
       </c>
       <c r="Z153" t="s" s="2">
-        <v>679</v>
+        <v>672</v>
       </c>
       <c r="AA153" t="s" s="2">
         <v>81</v>
@@ -21364,7 +21309,7 @@
         <v>81</v>
       </c>
       <c r="AF153" t="s" s="2">
-        <v>680</v>
+        <v>673</v>
       </c>
       <c r="AG153" t="s" s="2">
         <v>79</v>
@@ -21396,10 +21341,10 @@
     </row>
     <row r="154">
       <c r="A154" t="s" s="2">
-        <v>781</v>
+        <v>775</v>
       </c>
       <c r="B154" t="s" s="2">
-        <v>781</v>
+        <v>775</v>
       </c>
       <c r="C154" s="2"/>
       <c r="D154" t="s" s="2">
@@ -21422,16 +21367,16 @@
         <v>91</v>
       </c>
       <c r="K154" t="s" s="2">
-        <v>782</v>
+        <v>776</v>
       </c>
       <c r="L154" t="s" s="2">
-        <v>583</v>
+        <v>575</v>
       </c>
       <c r="M154" t="s" s="2">
-        <v>584</v>
+        <v>576</v>
       </c>
       <c r="N154" t="s" s="2">
-        <v>683</v>
+        <v>676</v>
       </c>
       <c r="O154" s="2"/>
       <c r="P154" t="s" s="2">
@@ -21481,7 +21426,7 @@
         <v>81</v>
       </c>
       <c r="AF154" t="s" s="2">
-        <v>684</v>
+        <v>677</v>
       </c>
       <c r="AG154" t="s" s="2">
         <v>79</v>
@@ -21502,21 +21447,21 @@
         <v>81</v>
       </c>
       <c r="AM154" t="s" s="2">
-        <v>685</v>
+        <v>678</v>
       </c>
       <c r="AN154" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AO154" t="s" s="2">
-        <v>686</v>
+        <v>679</v>
       </c>
     </row>
     <row r="155" hidden="true">
       <c r="A155" t="s" s="2">
-        <v>783</v>
+        <v>777</v>
       </c>
       <c r="B155" t="s" s="2">
-        <v>783</v>
+        <v>777</v>
       </c>
       <c r="C155" s="2"/>
       <c r="D155" t="s" s="2">
@@ -21542,13 +21487,13 @@
         <v>104</v>
       </c>
       <c r="L155" t="s" s="2">
-        <v>688</v>
+        <v>681</v>
       </c>
       <c r="M155" t="s" s="2">
-        <v>689</v>
+        <v>682</v>
       </c>
       <c r="N155" t="s" s="2">
-        <v>690</v>
+        <v>683</v>
       </c>
       <c r="O155" s="2"/>
       <c r="P155" t="s" s="2">
@@ -21598,7 +21543,7 @@
         <v>81</v>
       </c>
       <c r="AF155" t="s" s="2">
-        <v>691</v>
+        <v>684</v>
       </c>
       <c r="AG155" t="s" s="2">
         <v>79</v>
@@ -21630,10 +21575,10 @@
     </row>
     <row r="156" hidden="true">
       <c r="A156" t="s" s="2">
-        <v>784</v>
+        <v>778</v>
       </c>
       <c r="B156" t="s" s="2">
-        <v>784</v>
+        <v>778</v>
       </c>
       <c r="C156" s="2"/>
       <c r="D156" t="s" s="2">
@@ -21656,17 +21601,17 @@
         <v>91</v>
       </c>
       <c r="K156" t="s" s="2">
-        <v>363</v>
+        <v>358</v>
       </c>
       <c r="L156" t="s" s="2">
-        <v>785</v>
+        <v>779</v>
       </c>
       <c r="M156" t="s" s="2">
-        <v>786</v>
+        <v>780</v>
       </c>
       <c r="N156" s="2"/>
       <c r="O156" t="s" s="2">
-        <v>787</v>
+        <v>781</v>
       </c>
       <c r="P156" t="s" s="2">
         <v>81</v>
@@ -21715,7 +21660,7 @@
         <v>81</v>
       </c>
       <c r="AF156" t="s" s="2">
-        <v>784</v>
+        <v>778</v>
       </c>
       <c r="AG156" t="s" s="2">
         <v>79</v>
@@ -21730,27 +21675,27 @@
         <v>102</v>
       </c>
       <c r="AK156" t="s" s="2">
-        <v>788</v>
+        <v>782</v>
       </c>
       <c r="AL156" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AM156" t="s" s="2">
-        <v>789</v>
+        <v>783</v>
       </c>
       <c r="AN156" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AO156" t="s" s="2">
-        <v>686</v>
+        <v>679</v>
       </c>
     </row>
     <row r="157" hidden="true">
       <c r="A157" t="s" s="2">
-        <v>790</v>
+        <v>784</v>
       </c>
       <c r="B157" t="s" s="2">
-        <v>790</v>
+        <v>784</v>
       </c>
       <c r="C157" s="2"/>
       <c r="D157" t="s" s="2">
@@ -21773,16 +21718,16 @@
         <v>81</v>
       </c>
       <c r="K157" t="s" s="2">
-        <v>378</v>
+        <v>373</v>
       </c>
       <c r="L157" t="s" s="2">
-        <v>791</v>
+        <v>785</v>
       </c>
       <c r="M157" t="s" s="2">
-        <v>792</v>
+        <v>786</v>
       </c>
       <c r="N157" t="s" s="2">
-        <v>793</v>
+        <v>787</v>
       </c>
       <c r="O157" s="2"/>
       <c r="P157" t="s" s="2">
@@ -21811,10 +21756,10 @@
         <v>159</v>
       </c>
       <c r="Y157" t="s" s="2">
-        <v>794</v>
+        <v>788</v>
       </c>
       <c r="Z157" t="s" s="2">
-        <v>795</v>
+        <v>789</v>
       </c>
       <c r="AA157" t="s" s="2">
         <v>81</v>
@@ -21832,7 +21777,7 @@
         <v>81</v>
       </c>
       <c r="AF157" t="s" s="2">
-        <v>790</v>
+        <v>784</v>
       </c>
       <c r="AG157" t="s" s="2">
         <v>79</v>
@@ -21853,21 +21798,21 @@
         <v>81</v>
       </c>
       <c r="AM157" t="s" s="2">
-        <v>796</v>
+        <v>790</v>
       </c>
       <c r="AN157" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AO157" t="s" s="2">
-        <v>609</v>
+        <v>601</v>
       </c>
     </row>
     <row r="158" hidden="true">
       <c r="A158" t="s" s="2">
-        <v>797</v>
+        <v>791</v>
       </c>
       <c r="B158" t="s" s="2">
-        <v>797</v>
+        <v>791</v>
       </c>
       <c r="C158" s="2"/>
       <c r="D158" t="s" s="2">
@@ -21890,16 +21835,16 @@
         <v>81</v>
       </c>
       <c r="K158" t="s" s="2">
-        <v>798</v>
+        <v>792</v>
       </c>
       <c r="L158" t="s" s="2">
-        <v>799</v>
+        <v>793</v>
       </c>
       <c r="M158" t="s" s="2">
-        <v>800</v>
+        <v>794</v>
       </c>
       <c r="N158" t="s" s="2">
-        <v>705</v>
+        <v>698</v>
       </c>
       <c r="O158" s="2"/>
       <c r="P158" t="s" s="2">
@@ -21949,7 +21894,7 @@
         <v>81</v>
       </c>
       <c r="AF158" t="s" s="2">
-        <v>797</v>
+        <v>791</v>
       </c>
       <c r="AG158" t="s" s="2">
         <v>79</v>
@@ -21961,16 +21906,16 @@
         <v>152</v>
       </c>
       <c r="AJ158" t="s" s="2">
-        <v>423</v>
+        <v>653</v>
       </c>
       <c r="AK158" t="s" s="2">
-        <v>801</v>
+        <v>795</v>
       </c>
       <c r="AL158" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AM158" t="s" s="2">
-        <v>802</v>
+        <v>796</v>
       </c>
       <c r="AN158" t="s" s="2">
         <v>81</v>
@@ -21981,10 +21926,10 @@
     </row>
     <row r="159">
       <c r="A159" t="s" s="2">
-        <v>803</v>
+        <v>797</v>
       </c>
       <c r="B159" t="s" s="2">
-        <v>803</v>
+        <v>797</v>
       </c>
       <c r="C159" s="2"/>
       <c r="D159" t="s" s="2">
@@ -22007,16 +21952,16 @@
         <v>81</v>
       </c>
       <c r="K159" t="s" s="2">
-        <v>804</v>
+        <v>798</v>
       </c>
       <c r="L159" t="s" s="2">
-        <v>805</v>
+        <v>799</v>
       </c>
       <c r="M159" t="s" s="2">
-        <v>806</v>
+        <v>800</v>
       </c>
       <c r="N159" t="s" s="2">
-        <v>807</v>
+        <v>801</v>
       </c>
       <c r="O159" s="2"/>
       <c r="P159" t="s" s="2">
@@ -22066,7 +22011,7 @@
         <v>81</v>
       </c>
       <c r="AF159" t="s" s="2">
-        <v>803</v>
+        <v>797</v>
       </c>
       <c r="AG159" t="s" s="2">
         <v>79</v>
@@ -22081,13 +22026,13 @@
         <v>102</v>
       </c>
       <c r="AK159" t="s" s="2">
-        <v>808</v>
+        <v>802</v>
       </c>
       <c r="AL159" t="s" s="2">
-        <v>809</v>
+        <v>803</v>
       </c>
       <c r="AM159" t="s" s="2">
-        <v>810</v>
+        <v>804</v>
       </c>
       <c r="AN159" t="s" s="2">
         <v>81</v>
@@ -22098,10 +22043,10 @@
     </row>
     <row r="160" hidden="true">
       <c r="A160" t="s" s="2">
-        <v>811</v>
+        <v>805</v>
       </c>
       <c r="B160" t="s" s="2">
-        <v>811</v>
+        <v>805</v>
       </c>
       <c r="C160" s="2"/>
       <c r="D160" t="s" s="2">
@@ -22213,10 +22158,10 @@
     </row>
     <row r="161" hidden="true">
       <c r="A161" t="s" s="2">
-        <v>812</v>
+        <v>806</v>
       </c>
       <c r="B161" t="s" s="2">
-        <v>812</v>
+        <v>806</v>
       </c>
       <c r="C161" s="2"/>
       <c r="D161" t="s" s="2">
@@ -22330,10 +22275,10 @@
     </row>
     <row r="162" hidden="true">
       <c r="A162" t="s" s="2">
-        <v>813</v>
+        <v>807</v>
       </c>
       <c r="B162" t="s" s="2">
-        <v>813</v>
+        <v>807</v>
       </c>
       <c r="C162" s="2"/>
       <c r="D162" t="s" s="2">
@@ -22356,16 +22301,16 @@
         <v>91</v>
       </c>
       <c r="K162" t="s" s="2">
-        <v>814</v>
+        <v>808</v>
       </c>
       <c r="L162" t="s" s="2">
-        <v>815</v>
+        <v>809</v>
       </c>
       <c r="M162" t="s" s="2">
-        <v>816</v>
+        <v>810</v>
       </c>
       <c r="N162" t="s" s="2">
-        <v>817</v>
+        <v>811</v>
       </c>
       <c r="O162" s="2"/>
       <c r="P162" t="s" s="2">
@@ -22415,7 +22360,7 @@
         <v>81</v>
       </c>
       <c r="AF162" t="s" s="2">
-        <v>818</v>
+        <v>812</v>
       </c>
       <c r="AG162" t="s" s="2">
         <v>79</v>
@@ -22436,7 +22381,7 @@
         <v>81</v>
       </c>
       <c r="AM162" t="s" s="2">
-        <v>819</v>
+        <v>813</v>
       </c>
       <c r="AN162" t="s" s="2">
         <v>81</v>
@@ -22447,10 +22392,10 @@
     </row>
     <row r="163" hidden="true">
       <c r="A163" t="s" s="2">
-        <v>820</v>
+        <v>814</v>
       </c>
       <c r="B163" t="s" s="2">
-        <v>820</v>
+        <v>814</v>
       </c>
       <c r="C163" s="2"/>
       <c r="D163" t="s" s="2">
@@ -22473,13 +22418,13 @@
         <v>91</v>
       </c>
       <c r="K163" t="s" s="2">
-        <v>340</v>
+        <v>335</v>
       </c>
       <c r="L163" t="s" s="2">
-        <v>821</v>
+        <v>815</v>
       </c>
       <c r="M163" t="s" s="2">
-        <v>822</v>
+        <v>816</v>
       </c>
       <c r="N163" s="2"/>
       <c r="O163" s="2"/>
@@ -22530,7 +22475,7 @@
         <v>81</v>
       </c>
       <c r="AF163" t="s" s="2">
-        <v>823</v>
+        <v>817</v>
       </c>
       <c r="AG163" t="s" s="2">
         <v>79</v>
@@ -22551,7 +22496,7 @@
         <v>81</v>
       </c>
       <c r="AM163" t="s" s="2">
-        <v>824</v>
+        <v>818</v>
       </c>
       <c r="AN163" t="s" s="2">
         <v>81</v>
@@ -22562,10 +22507,10 @@
     </row>
     <row r="164">
       <c r="A164" t="s" s="2">
-        <v>825</v>
+        <v>819</v>
       </c>
       <c r="B164" t="s" s="2">
-        <v>825</v>
+        <v>819</v>
       </c>
       <c r="C164" s="2"/>
       <c r="D164" t="s" s="2">
@@ -22588,16 +22533,16 @@
         <v>91</v>
       </c>
       <c r="K164" t="s" s="2">
-        <v>556</v>
+        <v>548</v>
       </c>
       <c r="L164" t="s" s="2">
-        <v>826</v>
+        <v>820</v>
       </c>
       <c r="M164" t="s" s="2">
-        <v>827</v>
+        <v>821</v>
       </c>
       <c r="N164" t="s" s="2">
-        <v>828</v>
+        <v>822</v>
       </c>
       <c r="O164" s="2"/>
       <c r="P164" t="s" s="2">
@@ -22647,7 +22592,7 @@
         <v>81</v>
       </c>
       <c r="AF164" t="s" s="2">
-        <v>829</v>
+        <v>823</v>
       </c>
       <c r="AG164" t="s" s="2">
         <v>90</v>
@@ -22668,7 +22613,7 @@
         <v>81</v>
       </c>
       <c r="AM164" t="s" s="2">
-        <v>830</v>
+        <v>824</v>
       </c>
       <c r="AN164" t="s" s="2">
         <v>81</v>
@@ -22679,10 +22624,10 @@
     </row>
     <row r="165">
       <c r="A165" t="s" s="2">
-        <v>831</v>
+        <v>825</v>
       </c>
       <c r="B165" t="s" s="2">
-        <v>831</v>
+        <v>825</v>
       </c>
       <c r="C165" s="2"/>
       <c r="D165" t="s" s="2">
@@ -22705,16 +22650,16 @@
         <v>81</v>
       </c>
       <c r="K165" t="s" s="2">
-        <v>832</v>
+        <v>826</v>
       </c>
       <c r="L165" t="s" s="2">
-        <v>833</v>
+        <v>827</v>
       </c>
       <c r="M165" t="s" s="2">
-        <v>833</v>
+        <v>827</v>
       </c>
       <c r="N165" t="s" s="2">
-        <v>834</v>
+        <v>828</v>
       </c>
       <c r="O165" s="2"/>
       <c r="P165" t="s" s="2">
@@ -22764,7 +22709,7 @@
         <v>81</v>
       </c>
       <c r="AF165" t="s" s="2">
-        <v>831</v>
+        <v>825</v>
       </c>
       <c r="AG165" t="s" s="2">
         <v>79</v>
@@ -22773,19 +22718,19 @@
         <v>80</v>
       </c>
       <c r="AI165" t="s" s="2">
-        <v>81</v>
+        <v>152</v>
       </c>
       <c r="AJ165" t="s" s="2">
-        <v>835</v>
+        <v>829</v>
       </c>
       <c r="AK165" t="s" s="2">
-        <v>836</v>
+        <v>830</v>
       </c>
       <c r="AL165" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AM165" t="s" s="2">
-        <v>837</v>
+        <v>831</v>
       </c>
       <c r="AN165" t="s" s="2">
         <v>81</v>
@@ -22796,10 +22741,10 @@
     </row>
     <row r="166">
       <c r="A166" t="s" s="2">
-        <v>838</v>
+        <v>832</v>
       </c>
       <c r="B166" t="s" s="2">
-        <v>838</v>
+        <v>832</v>
       </c>
       <c r="C166" s="2"/>
       <c r="D166" t="s" s="2">
@@ -22822,13 +22767,13 @@
         <v>81</v>
       </c>
       <c r="K166" t="s" s="2">
-        <v>839</v>
+        <v>833</v>
       </c>
       <c r="L166" t="s" s="2">
-        <v>840</v>
+        <v>834</v>
       </c>
       <c r="M166" t="s" s="2">
-        <v>841</v>
+        <v>835</v>
       </c>
       <c r="N166" s="2"/>
       <c r="O166" s="2"/>
@@ -22879,7 +22824,7 @@
         <v>81</v>
       </c>
       <c r="AF166" t="s" s="2">
-        <v>838</v>
+        <v>832</v>
       </c>
       <c r="AG166" t="s" s="2">
         <v>79</v>
@@ -22897,10 +22842,10 @@
         <v>81</v>
       </c>
       <c r="AL166" t="s" s="2">
-        <v>842</v>
+        <v>836</v>
       </c>
       <c r="AM166" t="s" s="2">
-        <v>843</v>
+        <v>837</v>
       </c>
       <c r="AN166" t="s" s="2">
         <v>81</v>
@@ -22911,10 +22856,10 @@
     </row>
     <row r="167" hidden="true">
       <c r="A167" t="s" s="2">
-        <v>844</v>
+        <v>838</v>
       </c>
       <c r="B167" t="s" s="2">
-        <v>844</v>
+        <v>838</v>
       </c>
       <c r="C167" s="2"/>
       <c r="D167" t="s" s="2">
@@ -23026,10 +22971,10 @@
     </row>
     <row r="168" hidden="true">
       <c r="A168" t="s" s="2">
-        <v>845</v>
+        <v>839</v>
       </c>
       <c r="B168" t="s" s="2">
-        <v>845</v>
+        <v>839</v>
       </c>
       <c r="C168" s="2"/>
       <c r="D168" t="s" s="2">
@@ -23143,14 +23088,14 @@
     </row>
     <row r="169" hidden="true">
       <c r="A169" t="s" s="2">
-        <v>846</v>
+        <v>840</v>
       </c>
       <c r="B169" t="s" s="2">
-        <v>846</v>
+        <v>840</v>
       </c>
       <c r="C169" s="2"/>
       <c r="D169" t="s" s="2">
-        <v>847</v>
+        <v>841</v>
       </c>
       <c r="E169" s="2"/>
       <c r="F169" t="s" s="2">
@@ -23172,16 +23117,16 @@
         <v>111</v>
       </c>
       <c r="L169" t="s" s="2">
-        <v>848</v>
+        <v>842</v>
       </c>
       <c r="M169" t="s" s="2">
-        <v>849</v>
+        <v>843</v>
       </c>
       <c r="N169" t="s" s="2">
         <v>114</v>
       </c>
       <c r="O169" t="s" s="2">
-        <v>567</v>
+        <v>559</v>
       </c>
       <c r="P169" t="s" s="2">
         <v>81</v>
@@ -23230,7 +23175,7 @@
         <v>81</v>
       </c>
       <c r="AF169" t="s" s="2">
-        <v>850</v>
+        <v>844</v>
       </c>
       <c r="AG169" t="s" s="2">
         <v>79</v>
@@ -23262,10 +23207,10 @@
     </row>
     <row r="170" hidden="true">
       <c r="A170" t="s" s="2">
-        <v>851</v>
+        <v>845</v>
       </c>
       <c r="B170" t="s" s="2">
-        <v>851</v>
+        <v>845</v>
       </c>
       <c r="C170" s="2"/>
       <c r="D170" t="s" s="2">
@@ -23288,16 +23233,16 @@
         <v>81</v>
       </c>
       <c r="K170" t="s" s="2">
-        <v>839</v>
+        <v>833</v>
       </c>
       <c r="L170" t="s" s="2">
-        <v>852</v>
+        <v>846</v>
       </c>
       <c r="M170" t="s" s="2">
-        <v>853</v>
+        <v>847</v>
       </c>
       <c r="N170" t="s" s="2">
-        <v>854</v>
+        <v>848</v>
       </c>
       <c r="O170" s="2"/>
       <c r="P170" t="s" s="2">
@@ -23347,7 +23292,7 @@
         <v>81</v>
       </c>
       <c r="AF170" t="s" s="2">
-        <v>851</v>
+        <v>845</v>
       </c>
       <c r="AG170" t="s" s="2">
         <v>79</v>
@@ -23368,7 +23313,7 @@
         <v>81</v>
       </c>
       <c r="AM170" t="s" s="2">
-        <v>855</v>
+        <v>849</v>
       </c>
       <c r="AN170" t="s" s="2">
         <v>81</v>
@@ -23379,10 +23324,10 @@
     </row>
     <row r="171" hidden="true">
       <c r="A171" t="s" s="2">
-        <v>856</v>
+        <v>850</v>
       </c>
       <c r="B171" t="s" s="2">
-        <v>856</v>
+        <v>850</v>
       </c>
       <c r="C171" s="2"/>
       <c r="D171" t="s" s="2">
@@ -23494,10 +23439,10 @@
     </row>
     <row r="172" hidden="true">
       <c r="A172" t="s" s="2">
-        <v>857</v>
+        <v>851</v>
       </c>
       <c r="B172" t="s" s="2">
-        <v>857</v>
+        <v>851</v>
       </c>
       <c r="C172" s="2"/>
       <c r="D172" t="s" s="2">
@@ -23611,14 +23556,14 @@
     </row>
     <row r="173" hidden="true">
       <c r="A173" t="s" s="2">
-        <v>858</v>
+        <v>852</v>
       </c>
       <c r="B173" t="s" s="2">
-        <v>858</v>
+        <v>852</v>
       </c>
       <c r="C173" s="2"/>
       <c r="D173" t="s" s="2">
-        <v>847</v>
+        <v>841</v>
       </c>
       <c r="E173" s="2"/>
       <c r="F173" t="s" s="2">
@@ -23640,16 +23585,16 @@
         <v>111</v>
       </c>
       <c r="L173" t="s" s="2">
-        <v>848</v>
+        <v>842</v>
       </c>
       <c r="M173" t="s" s="2">
-        <v>849</v>
+        <v>843</v>
       </c>
       <c r="N173" t="s" s="2">
         <v>114</v>
       </c>
       <c r="O173" t="s" s="2">
-        <v>567</v>
+        <v>559</v>
       </c>
       <c r="P173" t="s" s="2">
         <v>81</v>
@@ -23698,7 +23643,7 @@
         <v>81</v>
       </c>
       <c r="AF173" t="s" s="2">
-        <v>850</v>
+        <v>844</v>
       </c>
       <c r="AG173" t="s" s="2">
         <v>79</v>
@@ -23730,10 +23675,10 @@
     </row>
     <row r="174" hidden="true">
       <c r="A174" t="s" s="2">
-        <v>859</v>
+        <v>853</v>
       </c>
       <c r="B174" t="s" s="2">
-        <v>859</v>
+        <v>853</v>
       </c>
       <c r="C174" s="2"/>
       <c r="D174" t="s" s="2">
@@ -23756,16 +23701,16 @@
         <v>81</v>
       </c>
       <c r="K174" t="s" s="2">
-        <v>860</v>
+        <v>854</v>
       </c>
       <c r="L174" t="s" s="2">
-        <v>861</v>
+        <v>855</v>
       </c>
       <c r="M174" t="s" s="2">
-        <v>862</v>
+        <v>856</v>
       </c>
       <c r="N174" t="s" s="2">
-        <v>248</v>
+        <v>857</v>
       </c>
       <c r="O174" s="2"/>
       <c r="P174" t="s" s="2">
@@ -23815,7 +23760,7 @@
         <v>81</v>
       </c>
       <c r="AF174" t="s" s="2">
-        <v>859</v>
+        <v>853</v>
       </c>
       <c r="AG174" t="s" s="2">
         <v>79</v>
@@ -23827,7 +23772,7 @@
         <v>152</v>
       </c>
       <c r="AJ174" t="s" s="2">
-        <v>863</v>
+        <v>858</v>
       </c>
       <c r="AK174" t="s" s="2">
         <v>81</v>
@@ -23836,21 +23781,21 @@
         <v>81</v>
       </c>
       <c r="AM174" t="s" s="2">
-        <v>864</v>
+        <v>859</v>
       </c>
       <c r="AN174" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AO174" t="s" s="2">
-        <v>252</v>
+        <v>860</v>
       </c>
     </row>
     <row r="175" hidden="true">
       <c r="A175" t="s" s="2">
-        <v>865</v>
+        <v>861</v>
       </c>
       <c r="B175" t="s" s="2">
-        <v>865</v>
+        <v>861</v>
       </c>
       <c r="C175" s="2"/>
       <c r="D175" t="s" s="2">
@@ -23873,16 +23818,16 @@
         <v>81</v>
       </c>
       <c r="K175" t="s" s="2">
-        <v>866</v>
+        <v>862</v>
       </c>
       <c r="L175" t="s" s="2">
-        <v>867</v>
+        <v>863</v>
       </c>
       <c r="M175" t="s" s="2">
-        <v>868</v>
+        <v>864</v>
       </c>
       <c r="N175" t="s" s="2">
-        <v>248</v>
+        <v>857</v>
       </c>
       <c r="O175" s="2"/>
       <c r="P175" t="s" s="2">
@@ -23932,20 +23877,20 @@
         <v>81</v>
       </c>
       <c r="AF175" t="s" s="2">
+        <v>861</v>
+      </c>
+      <c r="AG175" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH175" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="AI175" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AJ175" t="s" s="2">
         <v>865</v>
       </c>
-      <c r="AG175" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AH175" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="AI175" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AJ175" t="s" s="2">
-        <v>869</v>
-      </c>
       <c r="AK175" t="s" s="2">
         <v>81</v>
       </c>
@@ -23953,21 +23898,21 @@
         <v>81</v>
       </c>
       <c r="AM175" t="s" s="2">
-        <v>870</v>
+        <v>866</v>
       </c>
       <c r="AN175" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AO175" t="s" s="2">
-        <v>252</v>
+        <v>860</v>
       </c>
     </row>
     <row r="176" hidden="true">
       <c r="A176" t="s" s="2">
-        <v>871</v>
+        <v>867</v>
       </c>
       <c r="B176" t="s" s="2">
-        <v>871</v>
+        <v>867</v>
       </c>
       <c r="C176" s="2"/>
       <c r="D176" t="s" s="2">
@@ -23990,16 +23935,16 @@
         <v>81</v>
       </c>
       <c r="K176" t="s" s="2">
-        <v>866</v>
+        <v>862</v>
       </c>
       <c r="L176" t="s" s="2">
-        <v>872</v>
+        <v>868</v>
       </c>
       <c r="M176" t="s" s="2">
-        <v>873</v>
+        <v>869</v>
       </c>
       <c r="N176" t="s" s="2">
-        <v>248</v>
+        <v>857</v>
       </c>
       <c r="O176" s="2"/>
       <c r="P176" t="s" s="2">
@@ -24049,7 +23994,7 @@
         <v>81</v>
       </c>
       <c r="AF176" t="s" s="2">
-        <v>871</v>
+        <v>867</v>
       </c>
       <c r="AG176" t="s" s="2">
         <v>79</v>
@@ -24061,7 +24006,7 @@
         <v>81</v>
       </c>
       <c r="AJ176" t="s" s="2">
-        <v>869</v>
+        <v>865</v>
       </c>
       <c r="AK176" t="s" s="2">
         <v>81</v>
@@ -24070,21 +24015,21 @@
         <v>81</v>
       </c>
       <c r="AM176" t="s" s="2">
-        <v>870</v>
+        <v>866</v>
       </c>
       <c r="AN176" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AO176" t="s" s="2">
-        <v>252</v>
+        <v>860</v>
       </c>
     </row>
     <row r="177" hidden="true">
       <c r="A177" t="s" s="2">
-        <v>874</v>
+        <v>870</v>
       </c>
       <c r="B177" t="s" s="2">
-        <v>874</v>
+        <v>870</v>
       </c>
       <c r="C177" s="2"/>
       <c r="D177" t="s" s="2">
@@ -24107,19 +24052,19 @@
         <v>81</v>
       </c>
       <c r="K177" t="s" s="2">
-        <v>334</v>
+        <v>329</v>
       </c>
       <c r="L177" t="s" s="2">
-        <v>875</v>
+        <v>871</v>
       </c>
       <c r="M177" t="s" s="2">
-        <v>876</v>
+        <v>872</v>
       </c>
       <c r="N177" t="s" s="2">
-        <v>877</v>
+        <v>873</v>
       </c>
       <c r="O177" t="s" s="2">
-        <v>878</v>
+        <v>874</v>
       </c>
       <c r="P177" t="s" s="2">
         <v>81</v>
@@ -24168,7 +24113,7 @@
         <v>81</v>
       </c>
       <c r="AF177" t="s" s="2">
-        <v>874</v>
+        <v>870</v>
       </c>
       <c r="AG177" t="s" s="2">
         <v>79</v>
@@ -24180,30 +24125,30 @@
         <v>152</v>
       </c>
       <c r="AJ177" t="s" s="2">
-        <v>413</v>
+        <v>875</v>
       </c>
       <c r="AK177" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AL177" t="s" s="2">
-        <v>879</v>
+        <v>876</v>
       </c>
       <c r="AM177" t="s" s="2">
-        <v>880</v>
+        <v>877</v>
       </c>
       <c r="AN177" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AO177" t="s" s="2">
-        <v>881</v>
+        <v>878</v>
       </c>
     </row>
     <row r="178" hidden="true">
       <c r="A178" t="s" s="2">
-        <v>882</v>
+        <v>879</v>
       </c>
       <c r="B178" t="s" s="2">
-        <v>882</v>
+        <v>879</v>
       </c>
       <c r="C178" s="2"/>
       <c r="D178" t="s" s="2">
@@ -24226,16 +24171,16 @@
         <v>81</v>
       </c>
       <c r="K178" t="s" s="2">
+        <v>880</v>
+      </c>
+      <c r="L178" t="s" s="2">
+        <v>881</v>
+      </c>
+      <c r="M178" t="s" s="2">
+        <v>882</v>
+      </c>
+      <c r="N178" t="s" s="2">
         <v>883</v>
-      </c>
-      <c r="L178" t="s" s="2">
-        <v>884</v>
-      </c>
-      <c r="M178" t="s" s="2">
-        <v>885</v>
-      </c>
-      <c r="N178" t="s" s="2">
-        <v>886</v>
       </c>
       <c r="O178" s="2"/>
       <c r="P178" t="s" s="2">
@@ -24285,7 +24230,7 @@
         <v>81</v>
       </c>
       <c r="AF178" t="s" s="2">
-        <v>882</v>
+        <v>879</v>
       </c>
       <c r="AG178" t="s" s="2">
         <v>79</v>
@@ -24303,24 +24248,24 @@
         <v>81</v>
       </c>
       <c r="AL178" t="s" s="2">
-        <v>887</v>
+        <v>884</v>
       </c>
       <c r="AM178" t="s" s="2">
-        <v>888</v>
+        <v>885</v>
       </c>
       <c r="AN178" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AO178" t="s" s="2">
-        <v>889</v>
+        <v>886</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="s" s="2">
-        <v>890</v>
+        <v>887</v>
       </c>
       <c r="B179" t="s" s="2">
-        <v>890</v>
+        <v>887</v>
       </c>
       <c r="C179" s="2"/>
       <c r="D179" t="s" s="2">
@@ -24343,16 +24288,16 @@
         <v>81</v>
       </c>
       <c r="K179" t="s" s="2">
-        <v>860</v>
+        <v>854</v>
       </c>
       <c r="L179" t="s" s="2">
-        <v>891</v>
+        <v>888</v>
       </c>
       <c r="M179" t="s" s="2">
-        <v>892</v>
+        <v>889</v>
       </c>
       <c r="N179" t="s" s="2">
-        <v>248</v>
+        <v>857</v>
       </c>
       <c r="O179" s="2"/>
       <c r="P179" t="s" s="2">
@@ -24402,7 +24347,7 @@
         <v>81</v>
       </c>
       <c r="AF179" t="s" s="2">
-        <v>890</v>
+        <v>887</v>
       </c>
       <c r="AG179" t="s" s="2">
         <v>79</v>
@@ -24414,30 +24359,30 @@
         <v>152</v>
       </c>
       <c r="AJ179" t="s" s="2">
-        <v>863</v>
+        <v>858</v>
       </c>
       <c r="AK179" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AL179" t="s" s="2">
-        <v>893</v>
+        <v>890</v>
       </c>
       <c r="AM179" t="s" s="2">
-        <v>894</v>
+        <v>891</v>
       </c>
       <c r="AN179" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AO179" t="s" s="2">
-        <v>895</v>
+        <v>892</v>
       </c>
     </row>
     <row r="180" hidden="true">
       <c r="A180" t="s" s="2">
-        <v>896</v>
+        <v>893</v>
       </c>
       <c r="B180" t="s" s="2">
-        <v>896</v>
+        <v>893</v>
       </c>
       <c r="C180" s="2"/>
       <c r="D180" t="s" s="2">
@@ -24549,10 +24494,10 @@
     </row>
     <row r="181" hidden="true">
       <c r="A181" t="s" s="2">
-        <v>897</v>
+        <v>894</v>
       </c>
       <c r="B181" t="s" s="2">
-        <v>897</v>
+        <v>894</v>
       </c>
       <c r="C181" s="2"/>
       <c r="D181" t="s" s="2">
@@ -24666,10 +24611,10 @@
     </row>
     <row r="182">
       <c r="A182" t="s" s="2">
-        <v>898</v>
+        <v>895</v>
       </c>
       <c r="B182" t="s" s="2">
-        <v>898</v>
+        <v>895</v>
       </c>
       <c r="C182" s="2"/>
       <c r="D182" t="s" s="2">
@@ -24692,19 +24637,19 @@
         <v>91</v>
       </c>
       <c r="K182" t="s" s="2">
+        <v>256</v>
+      </c>
+      <c r="L182" t="s" s="2">
+        <v>896</v>
+      </c>
+      <c r="M182" t="s" s="2">
+        <v>896</v>
+      </c>
+      <c r="N182" t="s" s="2">
         <v>259</v>
       </c>
-      <c r="L182" t="s" s="2">
-        <v>899</v>
-      </c>
-      <c r="M182" t="s" s="2">
-        <v>899</v>
-      </c>
-      <c r="N182" t="s" s="2">
-        <v>262</v>
-      </c>
       <c r="O182" t="s" s="2">
-        <v>263</v>
+        <v>260</v>
       </c>
       <c r="P182" t="s" s="2">
         <v>81</v>
@@ -24753,7 +24698,7 @@
         <v>81</v>
       </c>
       <c r="AF182" t="s" s="2">
-        <v>264</v>
+        <v>261</v>
       </c>
       <c r="AG182" t="s" s="2">
         <v>79</v>
@@ -24774,21 +24719,21 @@
         <v>81</v>
       </c>
       <c r="AM182" t="s" s="2">
-        <v>265</v>
+        <v>262</v>
       </c>
       <c r="AN182" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AO182" t="s" s="2">
-        <v>266</v>
+        <v>263</v>
       </c>
     </row>
     <row r="183" hidden="true">
       <c r="A183" t="s" s="2">
-        <v>900</v>
+        <v>897</v>
       </c>
       <c r="B183" t="s" s="2">
-        <v>900</v>
+        <v>897</v>
       </c>
       <c r="C183" s="2"/>
       <c r="D183" t="s" s="2">
@@ -24814,65 +24759,65 @@
         <v>169</v>
       </c>
       <c r="L183" t="s" s="2">
-        <v>269</v>
+        <v>266</v>
       </c>
       <c r="M183" t="s" s="2">
-        <v>901</v>
+        <v>898</v>
       </c>
       <c r="N183" s="2"/>
       <c r="O183" t="s" s="2">
+        <v>268</v>
+      </c>
+      <c r="P183" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Q183" t="s" s="2">
+        <v>269</v>
+      </c>
+      <c r="R183" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="S183" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="T183" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="U183" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="V183" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="W183" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="X183" t="s" s="2">
+        <v>270</v>
+      </c>
+      <c r="Y183" t="s" s="2">
         <v>271</v>
       </c>
-      <c r="P183" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Q183" t="s" s="2">
+      <c r="Z183" t="s" s="2">
         <v>272</v>
       </c>
-      <c r="R183" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="S183" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="T183" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="U183" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="V183" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="W183" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="X183" t="s" s="2">
+      <c r="AA183" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AB183" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AC183" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AD183" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AE183" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AF183" t="s" s="2">
         <v>273</v>
-      </c>
-      <c r="Y183" t="s" s="2">
-        <v>274</v>
-      </c>
-      <c r="Z183" t="s" s="2">
-        <v>275</v>
-      </c>
-      <c r="AA183" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AB183" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AC183" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AD183" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AE183" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AF183" t="s" s="2">
-        <v>276</v>
       </c>
       <c r="AG183" t="s" s="2">
         <v>79</v>
@@ -24893,21 +24838,21 @@
         <v>81</v>
       </c>
       <c r="AM183" t="s" s="2">
-        <v>277</v>
+        <v>274</v>
       </c>
       <c r="AN183" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AO183" t="s" s="2">
-        <v>278</v>
+        <v>275</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="s" s="2">
-        <v>902</v>
+        <v>899</v>
       </c>
       <c r="B184" t="s" s="2">
-        <v>902</v>
+        <v>899</v>
       </c>
       <c r="C184" s="2"/>
       <c r="D184" t="s" s="2">
@@ -24933,14 +24878,14 @@
         <v>104</v>
       </c>
       <c r="L184" t="s" s="2">
-        <v>281</v>
+        <v>278</v>
       </c>
       <c r="M184" t="s" s="2">
-        <v>282</v>
+        <v>279</v>
       </c>
       <c r="N184" s="2"/>
       <c r="O184" t="s" s="2">
-        <v>284</v>
+        <v>280</v>
       </c>
       <c r="P184" t="s" s="2">
         <v>81</v>
@@ -24989,7 +24934,7 @@
         <v>81</v>
       </c>
       <c r="AF184" t="s" s="2">
-        <v>285</v>
+        <v>281</v>
       </c>
       <c r="AG184" t="s" s="2">
         <v>79</v>
@@ -25010,21 +24955,21 @@
         <v>81</v>
       </c>
       <c r="AM184" t="s" s="2">
-        <v>286</v>
+        <v>282</v>
       </c>
       <c r="AN184" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AO184" t="s" s="2">
-        <v>287</v>
+        <v>283</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="s" s="2">
-        <v>903</v>
+        <v>900</v>
       </c>
       <c r="B185" t="s" s="2">
-        <v>903</v>
+        <v>900</v>
       </c>
       <c r="C185" s="2"/>
       <c r="D185" t="s" s="2">
@@ -25050,14 +24995,14 @@
         <v>132</v>
       </c>
       <c r="L185" t="s" s="2">
-        <v>290</v>
+        <v>286</v>
       </c>
       <c r="M185" t="s" s="2">
-        <v>291</v>
+        <v>287</v>
       </c>
       <c r="N185" s="2"/>
       <c r="O185" t="s" s="2">
-        <v>293</v>
+        <v>288</v>
       </c>
       <c r="P185" t="s" s="2">
         <v>81</v>
@@ -25067,7 +25012,7 @@
         <v>81</v>
       </c>
       <c r="S185" t="s" s="2">
-        <v>904</v>
+        <v>901</v>
       </c>
       <c r="T185" t="s" s="2">
         <v>81</v>
@@ -25106,7 +25051,7 @@
         <v>81</v>
       </c>
       <c r="AF185" t="s" s="2">
-        <v>294</v>
+        <v>289</v>
       </c>
       <c r="AG185" t="s" s="2">
         <v>79</v>
@@ -25115,7 +25060,7 @@
         <v>90</v>
       </c>
       <c r="AI185" t="s" s="2">
-        <v>295</v>
+        <v>290</v>
       </c>
       <c r="AJ185" t="s" s="2">
         <v>102</v>
@@ -25127,21 +25072,21 @@
         <v>81</v>
       </c>
       <c r="AM185" t="s" s="2">
-        <v>296</v>
+        <v>291</v>
       </c>
       <c r="AN185" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AO185" t="s" s="2">
-        <v>287</v>
+        <v>283</v>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="s" s="2">
-        <v>905</v>
+        <v>902</v>
       </c>
       <c r="B186" t="s" s="2">
-        <v>905</v>
+        <v>902</v>
       </c>
       <c r="C186" s="2"/>
       <c r="D186" t="s" s="2">
@@ -25167,16 +25112,16 @@
         <v>169</v>
       </c>
       <c r="L186" t="s" s="2">
-        <v>299</v>
+        <v>294</v>
       </c>
       <c r="M186" t="s" s="2">
-        <v>300</v>
+        <v>295</v>
       </c>
       <c r="N186" t="s" s="2">
-        <v>301</v>
+        <v>296</v>
       </c>
       <c r="O186" t="s" s="2">
-        <v>302</v>
+        <v>297</v>
       </c>
       <c r="P186" t="s" s="2">
         <v>81</v>
@@ -25225,7 +25170,7 @@
         <v>81</v>
       </c>
       <c r="AF186" t="s" s="2">
-        <v>303</v>
+        <v>298</v>
       </c>
       <c r="AG186" t="s" s="2">
         <v>79</v>
@@ -25246,21 +25191,21 @@
         <v>81</v>
       </c>
       <c r="AM186" t="s" s="2">
-        <v>304</v>
+        <v>299</v>
       </c>
       <c r="AN186" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AO186" t="s" s="2">
-        <v>287</v>
+        <v>283</v>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="s" s="2">
-        <v>906</v>
+        <v>903</v>
       </c>
       <c r="B187" t="s" s="2">
-        <v>906</v>
+        <v>903</v>
       </c>
       <c r="C187" s="2"/>
       <c r="D187" t="s" s="2">
@@ -25283,16 +25228,16 @@
         <v>81</v>
       </c>
       <c r="K187" t="s" s="2">
-        <v>866</v>
+        <v>862</v>
       </c>
       <c r="L187" t="s" s="2">
-        <v>907</v>
+        <v>904</v>
       </c>
       <c r="M187" t="s" s="2">
-        <v>908</v>
+        <v>905</v>
       </c>
       <c r="N187" t="s" s="2">
-        <v>909</v>
+        <v>906</v>
       </c>
       <c r="O187" s="2"/>
       <c r="P187" t="s" s="2">
@@ -25342,7 +25287,7 @@
         <v>81</v>
       </c>
       <c r="AF187" t="s" s="2">
-        <v>906</v>
+        <v>903</v>
       </c>
       <c r="AG187" t="s" s="2">
         <v>79</v>
@@ -25354,30 +25299,30 @@
         <v>81</v>
       </c>
       <c r="AJ187" t="s" s="2">
-        <v>869</v>
+        <v>865</v>
       </c>
       <c r="AK187" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AL187" t="s" s="2">
-        <v>910</v>
+        <v>907</v>
       </c>
       <c r="AM187" t="s" s="2">
-        <v>911</v>
+        <v>908</v>
       </c>
       <c r="AN187" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AO187" t="s" s="2">
-        <v>252</v>
+        <v>860</v>
       </c>
     </row>
     <row r="188" hidden="true">
       <c r="A188" t="s" s="2">
-        <v>912</v>
+        <v>909</v>
       </c>
       <c r="B188" t="s" s="2">
-        <v>912</v>
+        <v>909</v>
       </c>
       <c r="C188" s="2"/>
       <c r="D188" t="s" s="2">
@@ -25400,16 +25345,16 @@
         <v>81</v>
       </c>
       <c r="K188" t="s" s="2">
-        <v>418</v>
+        <v>910</v>
       </c>
       <c r="L188" t="s" s="2">
-        <v>913</v>
+        <v>911</v>
       </c>
       <c r="M188" t="s" s="2">
-        <v>914</v>
+        <v>912</v>
       </c>
       <c r="N188" t="s" s="2">
-        <v>705</v>
+        <v>698</v>
       </c>
       <c r="O188" s="2"/>
       <c r="P188" t="s" s="2">
@@ -25459,7 +25404,7 @@
         <v>81</v>
       </c>
       <c r="AF188" t="s" s="2">
-        <v>912</v>
+        <v>909</v>
       </c>
       <c r="AG188" t="s" s="2">
         <v>79</v>
@@ -25471,7 +25416,7 @@
         <v>152</v>
       </c>
       <c r="AJ188" t="s" s="2">
-        <v>423</v>
+        <v>653</v>
       </c>
       <c r="AK188" t="s" s="2">
         <v>81</v>
@@ -25480,10 +25425,10 @@
         <v>81</v>
       </c>
       <c r="AM188" t="s" s="2">
-        <v>915</v>
+        <v>913</v>
       </c>
       <c r="AN188" t="s" s="2">
-        <v>742</v>
+        <v>735</v>
       </c>
       <c r="AO188" t="s" s="2">
         <v>81</v>
@@ -25491,10 +25436,10 @@
     </row>
     <row r="189">
       <c r="A189" t="s" s="2">
-        <v>916</v>
+        <v>914</v>
       </c>
       <c r="B189" t="s" s="2">
-        <v>916</v>
+        <v>914</v>
       </c>
       <c r="C189" s="2"/>
       <c r="D189" t="s" s="2">
@@ -25517,13 +25462,13 @@
         <v>81</v>
       </c>
       <c r="K189" t="s" s="2">
-        <v>839</v>
+        <v>833</v>
       </c>
       <c r="L189" t="s" s="2">
-        <v>917</v>
+        <v>915</v>
       </c>
       <c r="M189" t="s" s="2">
-        <v>918</v>
+        <v>916</v>
       </c>
       <c r="N189" s="2"/>
       <c r="O189" s="2"/>
@@ -25574,7 +25519,7 @@
         <v>81</v>
       </c>
       <c r="AF189" t="s" s="2">
-        <v>916</v>
+        <v>914</v>
       </c>
       <c r="AG189" t="s" s="2">
         <v>79</v>
@@ -25592,10 +25537,10 @@
         <v>81</v>
       </c>
       <c r="AL189" t="s" s="2">
-        <v>919</v>
+        <v>917</v>
       </c>
       <c r="AM189" t="s" s="2">
-        <v>920</v>
+        <v>918</v>
       </c>
       <c r="AN189" t="s" s="2">
         <v>81</v>
@@ -25606,10 +25551,10 @@
     </row>
     <row r="190" hidden="true">
       <c r="A190" t="s" s="2">
-        <v>921</v>
+        <v>919</v>
       </c>
       <c r="B190" t="s" s="2">
-        <v>921</v>
+        <v>919</v>
       </c>
       <c r="C190" s="2"/>
       <c r="D190" t="s" s="2">
@@ -25721,10 +25666,10 @@
     </row>
     <row r="191" hidden="true">
       <c r="A191" t="s" s="2">
-        <v>922</v>
+        <v>920</v>
       </c>
       <c r="B191" t="s" s="2">
-        <v>922</v>
+        <v>920</v>
       </c>
       <c r="C191" s="2"/>
       <c r="D191" t="s" s="2">
@@ -25838,14 +25783,14 @@
     </row>
     <row r="192" hidden="true">
       <c r="A192" t="s" s="2">
-        <v>923</v>
+        <v>921</v>
       </c>
       <c r="B192" t="s" s="2">
-        <v>923</v>
+        <v>921</v>
       </c>
       <c r="C192" s="2"/>
       <c r="D192" t="s" s="2">
-        <v>847</v>
+        <v>841</v>
       </c>
       <c r="E192" s="2"/>
       <c r="F192" t="s" s="2">
@@ -25867,16 +25812,16 @@
         <v>111</v>
       </c>
       <c r="L192" t="s" s="2">
-        <v>848</v>
+        <v>842</v>
       </c>
       <c r="M192" t="s" s="2">
-        <v>849</v>
+        <v>843</v>
       </c>
       <c r="N192" t="s" s="2">
         <v>114</v>
       </c>
       <c r="O192" t="s" s="2">
-        <v>567</v>
+        <v>559</v>
       </c>
       <c r="P192" t="s" s="2">
         <v>81</v>
@@ -25925,7 +25870,7 @@
         <v>81</v>
       </c>
       <c r="AF192" t="s" s="2">
-        <v>850</v>
+        <v>844</v>
       </c>
       <c r="AG192" t="s" s="2">
         <v>79</v>
@@ -25957,10 +25902,10 @@
     </row>
     <row r="193">
       <c r="A193" t="s" s="2">
-        <v>924</v>
+        <v>922</v>
       </c>
       <c r="B193" t="s" s="2">
-        <v>924</v>
+        <v>922</v>
       </c>
       <c r="C193" s="2"/>
       <c r="D193" t="s" s="2">
@@ -25986,13 +25931,13 @@
         <v>226</v>
       </c>
       <c r="L193" t="s" s="2">
+        <v>923</v>
+      </c>
+      <c r="M193" t="s" s="2">
+        <v>924</v>
+      </c>
+      <c r="N193" t="s" s="2">
         <v>925</v>
-      </c>
-      <c r="M193" t="s" s="2">
-        <v>926</v>
-      </c>
-      <c r="N193" t="s" s="2">
-        <v>927</v>
       </c>
       <c r="O193" s="2"/>
       <c r="P193" t="s" s="2">
@@ -26042,7 +25987,7 @@
         <v>81</v>
       </c>
       <c r="AF193" t="s" s="2">
-        <v>924</v>
+        <v>922</v>
       </c>
       <c r="AG193" t="s" s="2">
         <v>90</v>
@@ -26060,24 +26005,24 @@
         <v>81</v>
       </c>
       <c r="AL193" t="s" s="2">
-        <v>919</v>
+        <v>917</v>
       </c>
       <c r="AM193" t="s" s="2">
-        <v>928</v>
+        <v>926</v>
       </c>
       <c r="AN193" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AO193" t="s" s="2">
-        <v>929</v>
+        <v>927</v>
       </c>
     </row>
     <row r="194" hidden="true">
       <c r="A194" t="s" s="2">
-        <v>930</v>
+        <v>928</v>
       </c>
       <c r="B194" t="s" s="2">
-        <v>930</v>
+        <v>928</v>
       </c>
       <c r="C194" s="2"/>
       <c r="D194" t="s" s="2">
@@ -26100,16 +26045,16 @@
         <v>81</v>
       </c>
       <c r="K194" t="s" s="2">
-        <v>378</v>
+        <v>373</v>
       </c>
       <c r="L194" t="s" s="2">
+        <v>929</v>
+      </c>
+      <c r="M194" t="s" s="2">
+        <v>930</v>
+      </c>
+      <c r="N194" t="s" s="2">
         <v>931</v>
-      </c>
-      <c r="M194" t="s" s="2">
-        <v>932</v>
-      </c>
-      <c r="N194" t="s" s="2">
-        <v>933</v>
       </c>
       <c r="O194" s="2"/>
       <c r="P194" t="s" s="2">
@@ -26138,10 +26083,10 @@
         <v>159</v>
       </c>
       <c r="Y194" t="s" s="2">
-        <v>934</v>
+        <v>932</v>
       </c>
       <c r="Z194" t="s" s="2">
-        <v>935</v>
+        <v>933</v>
       </c>
       <c r="AA194" t="s" s="2">
         <v>81</v>
@@ -26159,7 +26104,7 @@
         <v>81</v>
       </c>
       <c r="AF194" t="s" s="2">
-        <v>930</v>
+        <v>928</v>
       </c>
       <c r="AG194" t="s" s="2">
         <v>79</v>
@@ -26177,24 +26122,24 @@
         <v>81</v>
       </c>
       <c r="AL194" t="s" s="2">
+        <v>934</v>
+      </c>
+      <c r="AM194" t="s" s="2">
+        <v>935</v>
+      </c>
+      <c r="AN194" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AO194" t="s" s="2">
         <v>936</v>
-      </c>
-      <c r="AM194" t="s" s="2">
-        <v>937</v>
-      </c>
-      <c r="AN194" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AO194" t="s" s="2">
-        <v>938</v>
       </c>
     </row>
     <row r="195" hidden="true">
       <c r="A195" t="s" s="2">
-        <v>939</v>
+        <v>937</v>
       </c>
       <c r="B195" t="s" s="2">
-        <v>939</v>
+        <v>937</v>
       </c>
       <c r="C195" s="2"/>
       <c r="D195" t="s" s="2">
@@ -26217,16 +26162,16 @@
         <v>81</v>
       </c>
       <c r="K195" t="s" s="2">
+        <v>938</v>
+      </c>
+      <c r="L195" t="s" s="2">
+        <v>939</v>
+      </c>
+      <c r="M195" t="s" s="2">
         <v>940</v>
       </c>
-      <c r="L195" t="s" s="2">
-        <v>941</v>
-      </c>
-      <c r="M195" t="s" s="2">
-        <v>942</v>
-      </c>
       <c r="N195" t="s" s="2">
-        <v>705</v>
+        <v>698</v>
       </c>
       <c r="O195" s="2"/>
       <c r="P195" t="s" s="2">
@@ -26276,7 +26221,7 @@
         <v>81</v>
       </c>
       <c r="AF195" t="s" s="2">
-        <v>939</v>
+        <v>937</v>
       </c>
       <c r="AG195" t="s" s="2">
         <v>79</v>
@@ -26288,16 +26233,16 @@
         <v>152</v>
       </c>
       <c r="AJ195" t="s" s="2">
-        <v>423</v>
+        <v>653</v>
       </c>
       <c r="AK195" t="s" s="2">
-        <v>943</v>
+        <v>941</v>
       </c>
       <c r="AL195" t="s" s="2">
-        <v>936</v>
+        <v>934</v>
       </c>
       <c r="AM195" t="s" s="2">
-        <v>944</v>
+        <v>942</v>
       </c>
       <c r="AN195" t="s" s="2">
         <v>81</v>
@@ -26308,14 +26253,14 @@
     </row>
     <row r="196" hidden="true">
       <c r="A196" t="s" s="2">
-        <v>945</v>
+        <v>943</v>
       </c>
       <c r="B196" t="s" s="2">
-        <v>945</v>
+        <v>943</v>
       </c>
       <c r="C196" s="2"/>
       <c r="D196" t="s" s="2">
-        <v>946</v>
+        <v>944</v>
       </c>
       <c r="E196" s="2"/>
       <c r="F196" t="s" s="2">
@@ -26334,16 +26279,16 @@
         <v>81</v>
       </c>
       <c r="K196" t="s" s="2">
+        <v>945</v>
+      </c>
+      <c r="L196" t="s" s="2">
+        <v>946</v>
+      </c>
+      <c r="M196" t="s" s="2">
         <v>947</v>
       </c>
-      <c r="L196" t="s" s="2">
+      <c r="N196" t="s" s="2">
         <v>948</v>
-      </c>
-      <c r="M196" t="s" s="2">
-        <v>949</v>
-      </c>
-      <c r="N196" t="s" s="2">
-        <v>950</v>
       </c>
       <c r="O196" s="2"/>
       <c r="P196" t="s" s="2">
@@ -26393,7 +26338,7 @@
         <v>81</v>
       </c>
       <c r="AF196" t="s" s="2">
-        <v>945</v>
+        <v>943</v>
       </c>
       <c r="AG196" t="s" s="2">
         <v>79</v>
@@ -26405,7 +26350,7 @@
         <v>152</v>
       </c>
       <c r="AJ196" t="s" s="2">
-        <v>423</v>
+        <v>653</v>
       </c>
       <c r="AK196" t="s" s="2">
         <v>81</v>
@@ -26414,7 +26359,7 @@
         <v>81</v>
       </c>
       <c r="AM196" t="s" s="2">
-        <v>951</v>
+        <v>949</v>
       </c>
       <c r="AN196" t="s" s="2">
         <v>81</v>
@@ -26425,10 +26370,10 @@
     </row>
     <row r="197" hidden="true">
       <c r="A197" t="s" s="2">
-        <v>952</v>
+        <v>950</v>
       </c>
       <c r="B197" t="s" s="2">
-        <v>952</v>
+        <v>950</v>
       </c>
       <c r="C197" s="2"/>
       <c r="D197" t="s" s="2">
@@ -26451,16 +26396,16 @@
         <v>81</v>
       </c>
       <c r="K197" t="s" s="2">
+        <v>951</v>
+      </c>
+      <c r="L197" t="s" s="2">
+        <v>952</v>
+      </c>
+      <c r="M197" t="s" s="2">
         <v>953</v>
       </c>
-      <c r="L197" t="s" s="2">
+      <c r="N197" t="s" s="2">
         <v>954</v>
-      </c>
-      <c r="M197" t="s" s="2">
-        <v>955</v>
-      </c>
-      <c r="N197" t="s" s="2">
-        <v>956</v>
       </c>
       <c r="O197" s="2"/>
       <c r="P197" t="s" s="2">
@@ -26510,7 +26455,7 @@
         <v>81</v>
       </c>
       <c r="AF197" t="s" s="2">
-        <v>952</v>
+        <v>950</v>
       </c>
       <c r="AG197" t="s" s="2">
         <v>79</v>
@@ -26522,16 +26467,16 @@
         <v>152</v>
       </c>
       <c r="AJ197" t="s" s="2">
-        <v>423</v>
+        <v>653</v>
       </c>
       <c r="AK197" t="s" s="2">
-        <v>957</v>
+        <v>955</v>
       </c>
       <c r="AL197" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AM197" t="s" s="2">
-        <v>958</v>
+        <v>956</v>
       </c>
       <c r="AN197" t="s" s="2">
         <v>81</v>
